--- a/feature_importance.xlsx
+++ b/feature_importance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4884110478462156</v>
+        <v>0.3818292590118642</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1621792593338677</v>
+        <v>0.1735443980434553</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1506388850489873</v>
+        <v>0.1479665613670646</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07064841293514204</v>
+        <v>0.0798524672027648</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04922518659937009</v>
+        <v>0.0621997808025555</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04078748784182543</v>
+        <v>0.05718639871460459</v>
       </c>
     </row>
     <row r="8">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006117755563948163</v>
+        <v>0.00810798987875609</v>
       </c>
     </row>
     <row r="9">
@@ -505,107 +505,1947 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.006016719878714214</v>
+        <v>0.008106659649882299</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug</t>
+          <t>cat__Calamity_Flood</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.003408696833579355</v>
+        <v>0.005353510800339413</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cat__Calamity_Flood</t>
+          <t>cat__Calamity_Drought</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.003292883469053487</v>
+        <v>0.004830497061768654</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids</t>
+          <t>cat__Calamity_Typhoon</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.002807810295122441</v>
+        <v>0.004697773530804322</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cat__Calamity_Typhoon</t>
+          <t>cat__Calamity_nan</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.002734111647209773</v>
+        <v>0.004223427731111867</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer</t>
+          <t>cat__Calamity_Landslide</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.002580722611505519</v>
+        <v>0.004221965839389114</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cat__Calamity_Landslide</t>
+          <t>cat__Pest_Rice Bug</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.002549077205867185</v>
+        <v>0.003470100690527945</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cat__Calamity_nan</t>
+          <t>cat__Pest_Aphids</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.002234460202290398</v>
+        <v>0.003331455324330816</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cat__Calamity_Drought</t>
+          <t>cat__Pest_Stem Borer</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.00219899517347842</v>
+        <v>0.003138438818812353</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cat__Pest_nan</t>
+          <t>cat__Pest_Armyworm</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.002134413133716198</v>
+        <v>0.002807100366809038</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm</t>
+          <t>cat__Pest_nan</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.002034074380106588</v>
+        <v>0.002731587738739115</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Aphids</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.001051746052375053</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.0008602547117126388</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.000827237762415267</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.0007822973537635331</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Aphids, Armyworm</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.0007595752812268792</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Aphids</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.0007136939093104203</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.0006724356972467946</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.0006534170628850341</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, None</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.0006449443421441195</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Aphids</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.0006430499665813125</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Armyworm</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.0006251356683658855</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Stem Borer, None</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.00061793257488432</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.0005808636179852094</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Aphids</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.000577057979637481</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Rice Bug, Aphids</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.0005684164549746287</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.0005502958061596927</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, None</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.0005458838707179253</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Armyworm</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.00054421001297334</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Rice Bug, Armyworm</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.0005404135058960243</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Stem Borer, Aphids</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.0005096425692557711</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Armyworm</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.0005087333792027387</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Rice Bug, Aphids</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.000502847130645025</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, None, Aphids</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.0004989685901919163</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, None</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.000484017803587094</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, None</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.0004568853073067632</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, None, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.0004528487292647555</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Stem Borer, None</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.000413856054251556</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.0004063788472935319</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Rice Bug, Armyworm, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.000404292303241582</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Stem Borer, Armyworm</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.0003896443369081115</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, None, Aphids</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.0003892411872661343</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Rice Bug, Aphids</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.000375424254801967</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Rice Bug, Stem Borer, Aphids</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.0003708492415981252</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, None, Armyworm, Aphids</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.0003623179266038942</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, None, Aphids, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.00035568820925487</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, None, Stem Borer, Armyworm</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.0003473822440002241</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Armyworm, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.0003469325870665246</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Armyworm, Aphids, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0.0003447136911123607</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Aphids, None, Armyworm</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.0003364592028536904</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Armyworm, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0.0003273435221124923</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, None, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0.0002947778542179248</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Stem Borer, Aphids, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0.0002910320786562304</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Aphids, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0.0002799261755334614</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Armyworm, Aphids, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0.0002797173857478152</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Stem Borer, Aphids, Armyworm</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0.0002772349835609884</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, None, Armyworm</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0.00027713724931661</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Rice Bug, Aphids, Armyworm</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0.0002764958802376993</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Armyworm, Aphids</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.0002761763412605334</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Aphids, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0.0002752820696816527</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Armyworm</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0.0002735799942799805</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, None, Armyworm</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.0002697988639014398</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Stem Borer, Aphids, None</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.0002670398875909636</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, None, Rice Bug, Armyworm</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.0002664497596191121</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Stem Borer, Armyworm, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0.0002659077772911718</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, None, Armyworm</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0.0002655635590438685</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Armyworm, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0.0002651949967275135</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Aphids, Armyworm, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.0002622923760898535</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Aphids, Rice Bug, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0.0002554514396584859</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Armyworm, None</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0.0002525120409962654</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, None, Aphids, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.000251750622554945</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Stem Borer, Armyworm</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0.0002421816465416962</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Aphids, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.0002352177474814157</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Stem Borer, Rice Bug, None</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0.0002309804546883716</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Stem Borer, Aphids, Armyworm</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0.0002302850033830721</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Armyworm, None</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0.0002267575948468102</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Aphids, None</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0.000226735842628935</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, None, Armyworm, Aphids</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0.0002256458261821855</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Armyworm, Aphids, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0.0002251350942544436</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Aphids, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0.0002246872392744566</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Stem Borer, Armyworm, Aphids</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0.0002226274213602614</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Rice Bug, Armyworm, Aphids</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0.0002215906310850215</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, None, Rice Bug, Armyworm</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0.000220079124229758</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Rice Bug, Armyworm, None</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0.0002141913319477592</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Rice Bug, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>0.00021402017125854</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Aphids, None</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0.000213938860333186</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Aphids, Armyworm</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0.000211337662861414</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Armyworm, Stem Borer, Aphids</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0.0002091938602558052</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Rice Bug, Armyworm</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>0.000208736989434746</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Aphids, Rice Bug, None</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0.0002075647269121039</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Armyworm, Rice Bug, Aphids</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0.0002028872283207163</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, None, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0.0002018556556504909</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, None, Aphids</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>0.0002014896442828844</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Aphids, Stem Borer, Armyworm</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>0.0002011352688353488</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, None, Aphids, Armyworm</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>0.000200682529662649</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, None, Rice Bug, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>0.0001997261537999476</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Rice Bug, None, Aphids</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>0.0001995847457147995</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Rice Bug, None</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>0.0001939100000177862</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Rice Bug, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>0.0001921507990201741</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Rice Bug, Armyworm, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>0.0001907508293108692</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Stem Borer, None, Aphids</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>0.0001893951907936171</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, None, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>0.0001859766825319058</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Rice Bug, Stem Borer, None</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0.0001819838796259871</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Armyworm, None</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0.0001762989298184533</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Armyworm, Aphids</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0.0001758798036042675</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Armyworm, Aphids</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0.0001749405714190214</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Stem Borer, Rice Bug, Armyworm</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>0.0001646605828696056</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Armyworm, Aphids, None</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0.000161320711340589</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Armyworm, None, Aphids</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>0.000160493594894387</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Rice Bug, None, Armyworm</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>0.0001588411130861191</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Rice Bug, Armyworm, Aphids</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>0.0001568146994743055</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Rice Bug, Stem Borer, Armyworm</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>0.0001566270834613724</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Armyworm, Rice Bug, Aphids</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>0.0001557036458470075</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Rice Bug, Armyworm</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>0.0001545263891571896</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Aphids, Armyworm, None</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>0.0001512540168673123</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Stem Borer, Aphids</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>0.00015116876315621</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Aphids, Armyworm</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>0.0001504017710397893</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Stem Borer, None</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0.0001484650887244796</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Rice Bug, Stem Borer, Armyworm</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0.000147951053962326</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, None, Stem Borer, Aphids</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>0.0001456679957657169</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, None, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0.0001436653860197606</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Stem Borer, Aphids, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>0.0001425382958480635</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Stem Borer, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>0.0001398889813804503</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, None, Stem Borer, Aphids</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>0.0001354692979655422</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Aphids, Armyworm, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>0.000131586934714279</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Armyworm, None, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>0.000130942460559701</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Rice Bug, Aphids, Armyworm</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>0.0001305181479279503</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Armyworm, Rice Bug, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>0.0001298017639997679</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Armyworm, Stem Borer, None</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>0.0001282400698886118</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Stem Borer, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>0.000128016017183606</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, None, Armyworm, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>0.0001252567621271507</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Rice Bug, Aphids, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>0.0001251220263585094</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Armyworm, None, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>0.0001245237833769664</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Stem Borer, Aphids, None</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>0.0001204277250737383</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Armyworm, Rice Bug, None</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>0.0001203318381744852</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Aphids, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>0.0001203267301058674</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Rice Bug, None, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>0.0001172638429900137</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Stem Borer, Rice Bug, Aphids</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>0.0001163366276294672</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, None, Aphids, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>0.0001157411600694419</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Stem Borer, None, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>0.0001155938465349619</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Stem Borer, Rice Bug, Armyworm</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>0.0001091157036776272</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Aphids, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>0.0001084064095279849</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Aphids, Armyworm, None</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>0.0001075842276242305</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Armyworm, None, Aphids</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>0.0001057773034554225</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Stem Borer, Rice Bug, None</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>0.0001054387981371076</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Armyworm, Stem Borer, None</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>0.0001052704582596025</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Rice Bug, None, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>0.0001024727889491962</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Aphids, Stem Borer, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>9.924466102923625e-05</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, None, Rice Bug, Aphids</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>9.828960888054881e-05</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, None, Stem Borer, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>9.784755406341663e-05</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Aphids, Stem Borer, Armyworm</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>9.647473680874073e-05</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Armyworm, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>9.624040080439191e-05</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, None, Rice Bug, Aphids</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>9.550940771042286e-05</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Armyworm, Aphids, None</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>9.355215060541662e-05</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Stem Borer, Armyworm, None</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>8.920943144514794e-05</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, None, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>8.866220423104944e-05</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Rice Bug, None, Aphids</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>8.450915933260668e-05</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, None, Rice Bug, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>8.342835624083672e-05</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Aphids, Rice Bug, Armyworm</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>8.330492928351147e-05</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Aphids, None, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>8.293037565003264e-05</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Stem Borer, None, Armyworm</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>8.247401105366509e-05</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Stem Borer, Armyworm, Aphids</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>8.151879917763832e-05</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Stem Borer, Aphids</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>8.120109711561377e-05</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Armyworm, None, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>7.749215957908481e-05</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Stem Borer, None, Aphids</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>7.551726883354148e-05</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Rice Bug, None, Armyworm</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>7.335947229116679e-05</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Armyworm, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>6.908633990098076e-05</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, None, Aphids, Armyworm</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>6.685621273845135e-05</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Stem Borer, None, Armyworm</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>6.424570843384135e-05</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Armyworm, Rice Bug, None</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>6.394468832876616e-05</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Rice Bug, Stem Borer, None</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>5.432405451746989e-05</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Aphids, Stem Borer, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>5.277963875480596e-05</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Rice Bug, Armyworm, None</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>5.273608006718426e-05</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Aphids, Rice Bug, None</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>5.159168116392555e-05</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, None, Armyworm, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>5.121846580931133e-05</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Aphids, Armyworm, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>4.971867174389377e-05</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Aphids, Stem Borer, None</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>4.9470862298246e-05</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Aphids, Rice Bug, Armyworm</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>4.846642349792685e-05</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Aphids, None, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>4.753927415538055e-05</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Armyworm, None, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>4.706422405826766e-05</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Stem Borer, None, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>4.635523387181221e-05</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Aphids, None, Armyworm</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>4.124582236980215e-05</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Aphids, Armyworm, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>4.069722708727879e-05</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Rice Bug, None</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>3.895977057616325e-05</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Rice Bug, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>3.759795936191979e-05</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Stem Borer, Armyworm</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>3.738143750496642e-05</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, None, Aphids, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>3.511430720453652e-05</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Rice Bug, Aphids, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>3.426771692125027e-05</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, None, Armyworm, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>3.278959430130549e-05</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Stem Borer, Armyworm, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>2.998916815764454e-05</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Aphids, Rice Bug, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>2.73148546038661e-05</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Armyworm, Stem Borer, Aphids</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>2.388705445313191e-05</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Rice Bug, None</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>2.151789207910455e-05</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, None, Armyworm, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>1.671869182446355e-05</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Armyworm, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>1.122346288216362e-05</v>
       </c>
     </row>
   </sheetData>

--- a/feature_importance.xlsx
+++ b/feature_importance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B203"/>
+  <dimension ref="A1:B201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,127 +435,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3818292590118642</v>
+        <v>0.4805116906843864</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>num__Income After</t>
+          <t>num__Crop Yield After</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1735443980434553</v>
+        <v>0.2100756338383808</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>num__Crop Yield After</t>
+          <t>num__Crop Yield Before</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1479665613670646</v>
+        <v>0.1211377286582241</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>num__Crop Yield Before</t>
+          <t>num__Farm Size (ha)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0798524672027648</v>
+        <v>0.08833365915606908</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>num__Income Before</t>
+          <t>cat__Subsidy Type_Fertilizer Subsidy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0621997808025555</v>
+        <v>0.008788344378516236</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>num__Farm Size (ha)</t>
+          <t>cat__Subsidy Type_Seed Subsidy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05718639871460459</v>
+        <v>0.008566712193584528</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cat__Subsidy Type_Seed Subsidy</t>
+          <t>cat__Calamity_Flood</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00810798987875609</v>
+        <v>0.004922302170144531</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cat__Subsidy Type_Fertilizer Subsidy</t>
+          <t>cat__Calamity_Typhoon</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008106659649882299</v>
+        <v>0.004345509593143879</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cat__Calamity_Flood</t>
+          <t>cat__Calamity_Landslide</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.005353510800339413</v>
+        <v>0.004209394641090301</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cat__Calamity_Drought</t>
+          <t>cat__Calamity_nan</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.004830497061768654</v>
+        <v>0.004124239976009894</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cat__Calamity_Typhoon</t>
+          <t>cat__Calamity_Drought</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.004697773530804322</v>
+        <v>0.00402099670284769</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cat__Calamity_nan</t>
+          <t>cat__Pest_Aphids</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.004223427731111867</v>
+        <v>0.002617168277394204</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cat__Calamity_Landslide</t>
+          <t>cat__Pest_Armyworm</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.004221965839389114</v>
+        <v>0.002437304377061722</v>
       </c>
     </row>
     <row r="15">
@@ -565,67 +565,67 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.003470100690527945</v>
+        <v>0.002344776050269097</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids</t>
+          <t>cat__Pest_Stem Borer</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.003331455324330816</v>
+        <v>0.002309293648155224</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer</t>
+          <t>cat__Pest_nan</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.003138438818812353</v>
+        <v>0.002131089349005432</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm</t>
+          <t>cat__Pest_None, Aphids, Armyworm</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.002807100366809038</v>
+        <v>0.001150691956473005</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cat__Pest_nan</t>
+          <t>cat__Pest_Armyworm, Aphids</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.002731587738739115</v>
+        <v>0.00107365130561234</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Aphids</t>
+          <t>cat__Pest_Armyworm, Rice Bug</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.001051746052375053</v>
+        <v>0.001009655592825959</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Rice Bug</t>
+          <t>cat__Pest_Armyworm, Stem Borer</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0008602547117126388</v>
+        <v>0.0009499167755686727</v>
       </c>
     </row>
     <row r="22">
@@ -635,1357 +635,1357 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.000827237762415267</v>
+        <v>0.000910707865291501</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Stem Borer</t>
+          <t>cat__Pest_None, Rice Bug</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0007822973537635331</v>
+        <v>0.0008944729863254991</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Aphids, Armyworm</t>
+          <t>cat__Pest_None, Aphids</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0007595752812268792</v>
+        <v>0.0007657506189867166</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Aphids</t>
+          <t>cat__Pest_Aphids, Armyworm</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0007136939093104203</v>
+        <v>0.0007545469635960729</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Rice Bug</t>
+          <t>cat__Pest_Stem Borer, Armyworm</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0006724356972467946</v>
+        <v>0.0007423822914979084</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Rice Bug</t>
+          <t>cat__Pest_Aphids, None</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0006534170628850341</v>
+        <v>0.0006684344979691162</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, None</t>
+          <t>cat__Pest_Aphids, Rice Bug</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0006449443421441195</v>
+        <v>0.000654964362791285</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Aphids</t>
+          <t>cat__Pest_Aphids, Stem Borer</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0006430499665813125</v>
+        <v>0.0006417632333505735</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Armyworm</t>
+          <t>cat__Pest_None, Rice Bug, Aphids</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0006251356683658855</v>
+        <v>0.0006261280462633315</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Stem Borer, None</t>
+          <t>cat__Pest_Stem Borer, None</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.00061793257488432</v>
+        <v>0.0006254996983877137</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Stem Borer</t>
+          <t>cat__Pest_Rice Bug, Stem Borer, Aphids</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0005808636179852094</v>
+        <v>0.0006238064297569266</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Aphids</t>
+          <t>cat__Pest_Armyworm, None, Aphids</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.000577057979637481</v>
+        <v>0.0006077681050146435</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Rice Bug, Aphids</t>
+          <t>cat__Pest_Stem Borer, None, Aphids</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0005684164549746287</v>
+        <v>0.0006006647024967024</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Stem Borer</t>
+          <t>cat__Pest_Rice Bug, Aphids</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0005502958061596927</v>
+        <v>0.0005946310952469303</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, None</t>
+          <t>cat__Pest_Stem Borer, Rice Bug, Aphids</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.0005458838707179253</v>
+        <v>0.0005701972844577709</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Armyworm</t>
+          <t>cat__Pest_None, Stem Borer, Armyworm</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.00054421001297334</v>
+        <v>0.0005584501341871413</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Rice Bug, Armyworm</t>
+          <t>cat__Pest_Rice Bug, Stem Borer</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.0005404135058960243</v>
+        <v>0.0005578265055202013</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Stem Borer, Aphids</t>
+          <t>cat__Pest_Stem Borer, Aphids, None, Armyworm</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.0005096425692557711</v>
+        <v>0.000545102129818794</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Armyworm</t>
+          <t>cat__Pest_None, Stem Borer, Aphids, Armyworm</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.0005087333792027387</v>
+        <v>0.0005394469642423518</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Rice Bug, Aphids</t>
+          <t>cat__Pest_Rice Bug, None</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.000502847130645025</v>
+        <v>0.0005226550913302513</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, None, Aphids</t>
+          <t>cat__Pest_Stem Borer, Aphids</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.0004989685901919163</v>
+        <v>0.0005196613035506297</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, None</t>
+          <t>cat__Pest_Rice Bug, Armyworm</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.000484017803587094</v>
+        <v>0.0005178128081806994</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, None</t>
+          <t>cat__Pest_Rice Bug, Stem Borer, None</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.0004568853073067632</v>
+        <v>0.0005002942615616993</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, None, Rice Bug</t>
+          <t>cat__Pest_Rice Bug, Armyworm, Stem Borer</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.0004528487292647555</v>
+        <v>0.0004982562499491243</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Stem Borer, None</t>
+          <t>cat__Pest_Stem Borer, Rice Bug</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.000413856054251556</v>
+        <v>0.0004894122381780088</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Rice Bug</t>
+          <t>cat__Pest_Armyworm, Rice Bug, Aphids</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0004063788472935319</v>
+        <v>0.0004873120516893501</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Rice Bug, Armyworm, Stem Borer</t>
+          <t>cat__Pest_Armyworm, Stem Borer, None</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.000404292303241582</v>
+        <v>0.0004861215838506107</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Stem Borer, Armyworm</t>
+          <t>cat__Pest_Armyworm, Rice Bug, Stem Borer, Aphids</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0003896443369081115</v>
+        <v>0.0004837394934728605</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, None, Aphids</t>
+          <t>cat__Pest_Armyworm, None</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.0003892411872661343</v>
+        <v>0.0004777800840643077</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Rice Bug, Aphids</t>
+          <t>cat__Pest_Aphids, Stem Borer, Armyworm, Rice Bug</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.000375424254801967</v>
+        <v>0.0004682151818963718</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Rice Bug, Stem Borer, Aphids</t>
+          <t>cat__Pest_Aphids, Rice Bug, Armyworm, Stem Borer</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.0003708492415981252</v>
+        <v>0.0004670305423314676</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, None, Armyworm, Aphids</t>
+          <t>cat__Pest_Stem Borer, Rice Bug, Armyworm</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.0003623179266038942</v>
+        <v>0.0004525837006957452</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, None, Aphids, Stem Borer</t>
+          <t>cat__Pest_None, Armyworm</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.00035568820925487</v>
+        <v>0.000447281996261914</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, None, Stem Borer, Armyworm</t>
+          <t>cat__Pest_Stem Borer, None, Rice Bug</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.0003473822440002241</v>
+        <v>0.0004460106840673973</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Armyworm, Stem Borer</t>
+          <t>cat__Pest_Stem Borer, Aphids, Armyworm, Rice Bug</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.0003469325870665246</v>
+        <v>0.0004448300622060463</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Armyworm, Aphids, Stem Borer</t>
+          <t>cat__Pest_Rice Bug, Aphids, None</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.0003447136911123607</v>
+        <v>0.00043882261306085</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Aphids, None, Armyworm</t>
+          <t>cat__Pest_Rice Bug, Aphids, Stem Borer</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.0003364592028536904</v>
+        <v>0.0004092628940832721</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Armyworm, Stem Borer</t>
+          <t>cat__Pest_Stem Borer, None, Armyworm</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.0003273435221124923</v>
+        <v>0.0003968729945482105</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, None, Stem Borer</t>
+          <t>cat__Pest_Stem Borer, None, Armyworm, Aphids</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.0002947778542179248</v>
+        <v>0.0003890412377943569</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Stem Borer, Aphids, Rice Bug</t>
+          <t>cat__Pest_Aphids, None, Stem Borer, Armyworm</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.0002910320786562304</v>
+        <v>0.0003842285607024329</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Aphids, Rice Bug</t>
+          <t>cat__Pest_Stem Borer, Rice Bug, Armyworm, Aphids</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.0002799261755334614</v>
+        <v>0.0003684005006426449</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Armyworm, Aphids, Rice Bug</t>
+          <t>cat__Pest_Stem Borer, Aphids, None</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.0002797173857478152</v>
+        <v>0.0003654787852390656</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Stem Borer, Aphids, Armyworm</t>
+          <t>cat__Pest_Rice Bug, None, Armyworm, Aphids</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.0002772349835609884</v>
+        <v>0.0003612062161029999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, None, Armyworm</t>
+          <t>cat__Pest_None, Armyworm, Rice Bug</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.00027713724931661</v>
+        <v>0.0003564921864098944</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Rice Bug, Aphids, Armyworm</t>
+          <t>cat__Pest_Aphids, None, Armyworm</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.0002764958802376993</v>
+        <v>0.0003563367274118559</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Armyworm, Aphids</t>
+          <t>cat__Pest_Aphids, Stem Borer, Rice Bug, Armyworm</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.0002761763412605334</v>
+        <v>0.0003561943555110225</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Aphids, Rice Bug</t>
+          <t>cat__Pest_None, Rice Bug, Aphids, Armyworm</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.0002752820696816527</v>
+        <v>0.0003523794500160261</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Armyworm</t>
+          <t>cat__Pest_Stem Borer, Rice Bug, Armyworm, None</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.0002735799942799805</v>
+        <v>0.0003496970062328566</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, None, Armyworm</t>
+          <t>cat__Pest_Stem Borer, Armyworm, None</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.0002697988639014398</v>
+        <v>0.000349690328765611</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Stem Borer, Aphids, None</t>
+          <t>cat__Pest_Rice Bug, None, Aphids</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.0002670398875909636</v>
+        <v>0.000341105891067886</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, None, Rice Bug, Armyworm</t>
+          <t>cat__Pest_Rice Bug, Aphids, Armyworm</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.0002664497596191121</v>
+        <v>0.0003375572106865224</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Stem Borer, Armyworm, Rice Bug</t>
+          <t>cat__Pest_Armyworm, Stem Borer, Aphids</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.0002659077772911718</v>
+        <v>0.0003188500775780332</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, None, Armyworm</t>
+          <t>cat__Pest_None, Aphids, Rice Bug, Stem Borer</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.0002655635590438685</v>
+        <v>0.0003120206857519895</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Armyworm, Rice Bug</t>
+          <t>cat__Pest_Aphids, Rice Bug, None</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.0002651949967275135</v>
+        <v>0.0003115471533905401</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Aphids, Armyworm, Rice Bug</t>
+          <t>cat__Pest_Armyworm, None, Stem Borer</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.0002622923760898535</v>
+        <v>0.0003013851287291981</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Aphids, Rice Bug, Stem Borer</t>
+          <t>cat__Pest_None, Rice Bug, Stem Borer</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.0002554514396584859</v>
+        <v>0.0002943317650454535</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Armyworm, None</t>
+          <t>cat__Pest_Armyworm, None, Aphids, Stem Borer</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.0002525120409962654</v>
+        <v>0.0002903763722945483</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, None, Aphids, Stem Borer</t>
+          <t>cat__Pest_None, Armyworm, Aphids, Stem Borer</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.000251750622554945</v>
+        <v>0.0002897435632609095</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Stem Borer, Armyworm</t>
+          <t>cat__Pest_None, Armyworm, Aphids, Rice Bug</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.0002421816465416962</v>
+        <v>0.0002773274613002487</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Aphids, Rice Bug</t>
+          <t>cat__Pest_Stem Borer, None, Rice Bug, Armyworm</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.0002352177474814157</v>
+        <v>0.0002658374611094291</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Stem Borer, Rice Bug, None</t>
+          <t>cat__Pest_None, Aphids, Rice Bug</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.0002309804546883716</v>
+        <v>0.0002636801745246313</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Stem Borer, Aphids, Armyworm</t>
+          <t>cat__Pest_Armyworm, None, Rice Bug</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.0002302850033830721</v>
+        <v>0.000261163052070872</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Armyworm, None</t>
+          <t>cat__Pest_None, Rice Bug, Armyworm, Aphids</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.0002267575948468102</v>
+        <v>0.0002541817088313096</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Aphids, None</t>
+          <t>cat__Pest_Armyworm, None, Rice Bug, Aphids</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.000226735842628935</v>
+        <v>0.0002533458561269561</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, None, Armyworm, Aphids</t>
+          <t>cat__Pest_Rice Bug, None, Aphids, Stem Borer</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.0002256458261821855</v>
+        <v>0.0002524783877316037</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Armyworm, Aphids, Stem Borer</t>
+          <t>cat__Pest_Rice Bug, Armyworm, Stem Borer, Aphids</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.0002251350942544436</v>
+        <v>0.0002523613018491513</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Aphids, Stem Borer</t>
+          <t>cat__Pest_None, Rice Bug, Armyworm</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.0002246872392744566</v>
+        <v>0.0002509545064879312</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Stem Borer, Armyworm, Aphids</t>
+          <t>cat__Pest_Rice Bug, Armyworm, Aphids, Stem Borer</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.0002226274213602614</v>
+        <v>0.0002480121746178102</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Rice Bug, Armyworm, Aphids</t>
+          <t>cat__Pest_None, Armyworm, Stem Borer</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.0002215906310850215</v>
+        <v>0.0002475997504171111</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, None, Rice Bug, Armyworm</t>
+          <t>cat__Pest_Stem Borer, Aphids, Armyworm, None</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.000220079124229758</v>
+        <v>0.0002418108855394456</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Rice Bug, Armyworm, None</t>
+          <t>cat__Pest_Stem Borer, Aphids, Rice Bug</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.0002141913319477592</v>
+        <v>0.0002237601373581382</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Rice Bug, Stem Borer</t>
+          <t>cat__Pest_Stem Borer, Armyworm, Aphids, None</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.00021402017125854</v>
+        <v>0.0002214886926846076</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Aphids, None</t>
+          <t>cat__Pest_Rice Bug, Aphids, Armyworm, Stem Borer</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.000213938860333186</v>
+        <v>0.0002213372218752584</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Aphids, Armyworm</t>
+          <t>cat__Pest_Rice Bug, Armyworm, None</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.000211337662861414</v>
+        <v>0.0002205829819757469</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Armyworm, Stem Borer, Aphids</t>
+          <t>cat__Pest_Aphids, Armyworm, None</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.0002091938602558052</v>
+        <v>0.0002193812515700006</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Rice Bug, Armyworm</t>
+          <t>cat__Pest_Armyworm, None, Rice Bug, Stem Borer</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.000208736989434746</v>
+        <v>0.0002187630488862446</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Aphids, Rice Bug, None</t>
+          <t>cat__Pest_None, Armyworm, Aphids</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.0002075647269121039</v>
+        <v>0.0002172037994953463</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Armyworm, Rice Bug, Aphids</t>
+          <t>cat__Pest_Stem Borer, Rice Bug, None, Aphids</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.0002028872283207163</v>
+        <v>0.0002171927084479166</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, None, Stem Borer</t>
+          <t>cat__Pest_Rice Bug, Stem Borer, None, Aphids</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.0002018556556504909</v>
+        <v>0.0002147763624261813</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, None, Aphids</t>
+          <t>cat__Pest_Rice Bug, Stem Borer, Aphids, None</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.0002014896442828844</v>
+        <v>0.0002047324313157798</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Aphids, Stem Borer, Armyworm</t>
+          <t>cat__Pest_Rice Bug, Stem Borer, Aphids, Armyworm</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.0002011352688353488</v>
+        <v>0.0001974288101481214</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, None, Aphids, Armyworm</t>
+          <t>cat__Pest_Rice Bug, None, Stem Borer</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.000200682529662649</v>
+        <v>0.000197353663189612</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, None, Rice Bug, Stem Borer</t>
+          <t>cat__Pest_Aphids, Stem Borer, None, Rice Bug</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.0001997261537999476</v>
+        <v>0.0001970997811763822</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Rice Bug, None, Aphids</t>
+          <t>cat__Pest_Stem Borer, Armyworm, Aphids</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.0001995847457147995</v>
+        <v>0.0001951179382496954</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Rice Bug, None</t>
+          <t>cat__Pest_Armyworm, Stem Borer, Aphids, None</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.0001939100000177862</v>
+        <v>0.0001934195534506383</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Rice Bug, Stem Borer</t>
+          <t>cat__Pest_Aphids, Rice Bug, Armyworm</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.0001921507990201741</v>
+        <v>0.0001929199515798703</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Rice Bug, Armyworm, Stem Borer</t>
+          <t>cat__Pest_Aphids, None, Rice Bug, Armyworm</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.0001907508293108692</v>
+        <v>0.0001928833333717703</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Stem Borer, None, Aphids</t>
+          <t>cat__Pest_Aphids, Armyworm, Stem Borer, None</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.0001893951907936171</v>
+        <v>0.0001923361872256562</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, None, Rice Bug</t>
+          <t>cat__Pest_Stem Borer, Armyworm, Rice Bug, Aphids</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.0001859766825319058</v>
+        <v>0.0001922282956753472</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Rice Bug, Stem Borer, None</t>
+          <t>cat__Pest_None, Armyworm, Rice Bug, Aphids</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.0001819838796259871</v>
+        <v>0.0001917712659213094</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Armyworm, None</t>
+          <t>cat__Pest_Rice Bug, Stem Borer, Armyworm, Aphids</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.0001762989298184533</v>
+        <v>0.0001908994921688251</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Armyworm, Aphids</t>
+          <t>cat__Pest_Stem Borer, Aphids, Rice Bug, None</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.0001758798036042675</v>
+        <v>0.0001899192797592899</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Armyworm, Aphids</t>
+          <t>cat__Pest_None, Aphids, Stem Borer, Armyworm</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.0001749405714190214</v>
+        <v>0.0001889780616079894</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Stem Borer, Rice Bug, Armyworm</t>
+          <t>cat__Pest_Aphids, Stem Borer, None</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.0001646605828696056</v>
+        <v>0.0001883085342605044</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Armyworm, Aphids, None</t>
+          <t>cat__Pest_Rice Bug, Armyworm, Aphids</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.000161320711340589</v>
+        <v>0.0001829820343587248</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Armyworm, None, Aphids</t>
+          <t>cat__Pest_Rice Bug, Aphids, Armyworm, None</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.000160493594894387</v>
+        <v>0.0001820311744243865</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Rice Bug, None, Armyworm</t>
+          <t>cat__Pest_Armyworm, Rice Bug, None, Stem Borer</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.0001588411130861191</v>
+        <v>0.0001752717628656713</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Rice Bug, Armyworm, Aphids</t>
+          <t>cat__Pest_Rice Bug, Aphids, Stem Borer, Armyworm</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.0001568146994743055</v>
+        <v>0.0001717609002568438</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Rice Bug, Stem Borer, Armyworm</t>
+          <t>cat__Pest_Stem Borer, Aphids, Rice Bug, Armyworm</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.0001566270834613724</v>
+        <v>0.0001698110023169601</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Armyworm, Rice Bug, Aphids</t>
+          <t>cat__Pest_Rice Bug, None, Armyworm</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.0001557036458470075</v>
+        <v>0.0001675690126288744</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Rice Bug, Armyworm</t>
+          <t>cat__Pest_Rice Bug, None, Stem Borer, Aphids</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.0001545263891571896</v>
+        <v>0.0001655400804360697</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Aphids, Armyworm, None</t>
+          <t>cat__Pest_Rice Bug, Stem Borer, Armyworm</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.0001512540168673123</v>
+        <v>0.0001651886266716899</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Stem Borer, Aphids</t>
+          <t>cat__Pest_Stem Borer, Aphids, Armyworm</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.00015116876315621</v>
+        <v>0.0001648301158976988</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Aphids, Armyworm</t>
+          <t>cat__Pest_Aphids, Rice Bug, Stem Borer</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.0001504017710397893</v>
+        <v>0.0001627807390064265</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Stem Borer, None</t>
+          <t>cat__Pest_Stem Borer, Rice Bug, Aphids, Armyworm</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.0001484650887244796</v>
+        <v>0.00016160595103038</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Rice Bug, Stem Borer, Armyworm</t>
+          <t>cat__Pest_Aphids, Rice Bug, None, Armyworm</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.000147951053962326</v>
+        <v>0.0001608289505770041</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, None, Stem Borer, Aphids</t>
+          <t>cat__Pest_Armyworm, Stem Borer, Rice Bug, None</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.0001456679957657169</v>
+        <v>0.0001604880965102918</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, None, Rice Bug</t>
+          <t>cat__Pest_Armyworm, Stem Borer, Rice Bug, Aphids</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.0001436653860197606</v>
+        <v>0.0001591669670442723</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Stem Borer, Aphids, Rice Bug</t>
+          <t>cat__Pest_Armyworm, Aphids, Stem Borer, Rice Bug</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.0001425382958480635</v>
+        <v>0.0001561218086078456</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Stem Borer, Rice Bug</t>
+          <t>cat__Pest_Armyworm, Aphids, Stem Borer</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.0001398889813804503</v>
+        <v>0.0001538458740797217</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, None, Stem Borer, Aphids</t>
+          <t>cat__Pest_Aphids, None, Rice Bug, Stem Borer</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.0001354692979655422</v>
+        <v>0.0001483435261574543</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Aphids, Armyworm, Stem Borer</t>
+          <t>cat__Pest_Stem Borer, Armyworm, Rice Bug, None</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.000131586934714279</v>
+        <v>0.0001429369242851029</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Armyworm, None, Rice Bug</t>
+          <t>cat__Pest_Armyworm, Aphids, Rice Bug</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.000130942460559701</v>
+        <v>0.0001425223458217002</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Rice Bug, Aphids, Armyworm</t>
+          <t>cat__Pest_Aphids, Rice Bug, None, Stem Borer</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.0001305181479279503</v>
+        <v>0.000141095589784364</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Armyworm, Rice Bug, Stem Borer</t>
+          <t>cat__Pest_None, Stem Borer, Armyworm, Aphids</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.0001298017639997679</v>
+        <v>0.0001387081779614268</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Armyworm, Stem Borer, None</t>
+          <t>cat__Pest_Aphids, Armyworm, Stem Borer</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.0001282400698886118</v>
+        <v>0.0001375123984221588</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Stem Borer, Rice Bug</t>
+          <t>cat__Pest_None, Rice Bug, Stem Borer, Armyworm</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.000128016017183606</v>
+        <v>0.0001355832943936967</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, None, Armyworm, Rice Bug</t>
+          <t>cat__Pest_Aphids, Stem Borer, Rice Bug, None</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.0001252567621271507</v>
+        <v>0.0001333250439148797</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Rice Bug, Aphids, Stem Borer</t>
+          <t>cat__Pest_Armyworm, Rice Bug, Stem Borer, None</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.0001251220263585094</v>
+        <v>0.0001310943583341602</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Armyworm, None, Stem Borer</t>
+          <t>cat__Pest_Armyworm, Stem Borer, Aphids, Rice Bug</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.0001245237833769664</v>
+        <v>0.0001303974495134227</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Stem Borer, Aphids, None</t>
+          <t>cat__Pest_None, Stem Borer, Rice Bug, Armyworm</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.0001204277250737383</v>
+        <v>0.0001268615765672975</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Armyworm, Rice Bug, None</t>
+          <t>cat__Pest_Rice Bug, Armyworm, Aphids, None</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.0001203318381744852</v>
+        <v>0.0001259602795441273</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Aphids, Stem Borer</t>
+          <t>cat__Pest_Stem Borer, Armyworm, Rice Bug</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.0001203267301058674</v>
+        <v>0.0001255331326133995</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Rice Bug, None, Stem Borer</t>
+          <t>cat__Pest_Aphids, None, Stem Borer</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.0001172638429900137</v>
+        <v>0.0001255216817387752</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Stem Borer, Rice Bug, Aphids</t>
+          <t>cat__Pest_Armyworm, Rice Bug, None, Aphids</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.0001163366276294672</v>
+        <v>0.0001248793998876363</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, None, Aphids, Rice Bug</t>
+          <t>cat__Pest_None, Stem Borer, Aphids</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.0001157411600694419</v>
+        <v>0.0001245973891270837</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Stem Borer, None, Rice Bug</t>
+          <t>cat__Pest_Stem Borer, None, Armyworm, Rice Bug</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.0001155938465349619</v>
+        <v>0.0001243606001851617</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Stem Borer, Rice Bug, Armyworm</t>
+          <t>cat__Pest_Stem Borer, None, Rice Bug, Aphids</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.0001091157036776272</v>
+        <v>0.000117208290348342</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Aphids, Stem Borer</t>
+          <t>cat__Pest_Stem Borer, Armyworm, None, Rice Bug</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.0001084064095279849</v>
+        <v>0.00011617643610334</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Aphids, Armyworm, None</t>
+          <t>cat__Pest_Armyworm, Aphids, None, Stem Borer</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.0001075842276242305</v>
+        <v>0.0001158112947380661</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Armyworm, None, Aphids</t>
+          <t>cat__Pest_Aphids, None, Rice Bug</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.0001057773034554225</v>
+        <v>0.0001157259618295161</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Stem Borer, Rice Bug, None</t>
+          <t>cat__Pest_Aphids, Rice Bug, Armyworm, None</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.0001054387981371076</v>
+        <v>0.0001155304594855683</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Armyworm, Stem Borer, None</t>
+          <t>cat__Pest_None, Aphids, Stem Borer, Rice Bug</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.0001052704582596025</v>
+        <v>0.0001134597855428206</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Rice Bug, None, Stem Borer</t>
+          <t>cat__Pest_Armyworm, Stem Borer, None, Aphids</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.0001024727889491962</v>
+        <v>0.0001121313200143646</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Aphids, Stem Borer, Rice Bug</t>
+          <t>cat__Pest_Rice Bug, Armyworm, None, Aphids</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>9.924466102923625e-05</v>
+        <v>0.0001097388577497324</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, None, Rice Bug, Aphids</t>
+          <t>cat__Pest_Armyworm, None, Stem Borer, Aphids</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>9.828960888054881e-05</v>
+        <v>0.0001080523225766881</v>
       </c>
     </row>
     <row r="158">
@@ -1995,387 +1995,387 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>9.784755406341663e-05</v>
+        <v>0.0001077887248452694</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Aphids, Stem Borer, Armyworm</t>
+          <t>cat__Pest_Rice Bug, Armyworm, None, Stem Borer</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>9.647473680874073e-05</v>
+        <v>0.0001077117599158344</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Armyworm, Rice Bug</t>
+          <t>cat__Pest_Stem Borer, None, Aphids, Rice Bug</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>9.624040080439191e-05</v>
+        <v>0.0001062261691351597</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, None, Rice Bug, Aphids</t>
+          <t>cat__Pest_Armyworm, Rice Bug, Stem Borer</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>9.550940771042286e-05</v>
+        <v>0.00010521646772756</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Armyworm, Aphids, None</t>
+          <t>cat__Pest_Stem Borer, Rice Bug, None, Armyworm</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>9.355215060541662e-05</v>
+        <v>0.0001049617757724417</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Stem Borer, Armyworm, None</t>
+          <t>cat__Pest_None, Stem Borer, Aphids, Rice Bug</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>8.920943144514794e-05</v>
+        <v>0.0001035576041427578</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, None, Stem Borer</t>
+          <t>cat__Pest_Stem Borer, Armyworm, None, Aphids</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>8.866220423104944e-05</v>
+        <v>0.0001005113245236022</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Rice Bug, None, Aphids</t>
+          <t>cat__Pest_Rice Bug, Armyworm, Stem Borer, None</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>8.450915933260668e-05</v>
+        <v>9.916705069585192e-05</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, None, Rice Bug, Stem Borer</t>
+          <t>cat__Pest_Aphids, Rice Bug, Stem Borer, Armyworm</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>8.342835624083672e-05</v>
+        <v>9.655264913422166e-05</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Aphids, Rice Bug, Armyworm</t>
+          <t>cat__Pest_None, Rice Bug, Aphids, Stem Borer</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>8.330492928351147e-05</v>
+        <v>9.41770408886878e-05</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Aphids, None, Stem Borer</t>
+          <t>cat__Pest_Aphids, Stem Borer, None, Armyworm</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>8.293037565003264e-05</v>
+        <v>9.196436966987092e-05</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Stem Borer, None, Armyworm</t>
+          <t>cat__Pest_None, Aphids, Rice Bug, Armyworm</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>8.247401105366509e-05</v>
+        <v>8.960792534842458e-05</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Stem Borer, Armyworm, Aphids</t>
+          <t>cat__Pest_Rice Bug, Stem Borer, None, Armyworm</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>8.151879917763832e-05</v>
+        <v>8.701096793328094e-05</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Stem Borer, Aphids</t>
+          <t>cat__Pest_Armyworm, Rice Bug, Aphids, Stem Borer</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>8.120109711561377e-05</v>
+        <v>8.556362112904411e-05</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Armyworm, None, Stem Borer</t>
+          <t>cat__Pest_None, Stem Borer, Rice Bug</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>7.749215957908481e-05</v>
+        <v>8.41324580573003e-05</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Stem Borer, None, Aphids</t>
+          <t>cat__Pest_Aphids, Stem Borer, Rice Bug</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>7.551726883354148e-05</v>
+        <v>8.167752689958161e-05</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Rice Bug, None, Armyworm</t>
+          <t>cat__Pest_None, Armyworm, Rice Bug, Stem Borer</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>7.335947229116679e-05</v>
+        <v>7.931410296825779e-05</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Armyworm, Stem Borer</t>
+          <t>cat__Pest_Rice Bug, Stem Borer, Armyworm, None</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>6.908633990098076e-05</v>
+        <v>7.526159766431289e-05</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, None, Aphids, Armyworm</t>
+          <t>cat__Pest_Aphids, Armyworm, None, Stem Borer</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>6.685621273845135e-05</v>
+        <v>7.275352732577198e-05</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Stem Borer, None, Armyworm</t>
+          <t>cat__Pest_Armyworm, Rice Bug, None</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>6.424570843384135e-05</v>
+        <v>6.889933955715963e-05</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Armyworm, Rice Bug, None</t>
+          <t>cat__Pest_Aphids, Armyworm, None, Rice Bug</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>6.394468832876616e-05</v>
+        <v>6.825970296698002e-05</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Rice Bug, Stem Borer, None</t>
+          <t>cat__Pest_Rice Bug, None, Aphids, Armyworm</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>5.432405451746989e-05</v>
+        <v>6.419514303421773e-05</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Aphids, Stem Borer, Rice Bug</t>
+          <t>cat__Pest_Aphids, Armyworm, Rice Bug, None</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>5.277963875480596e-05</v>
+        <v>6.218215208331202e-05</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Rice Bug, Armyworm, None</t>
+          <t>cat__Pest_Aphids, Stem Borer, Armyworm</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>5.273608006718426e-05</v>
+        <v>6.081276568075594e-05</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Aphids, Rice Bug, None</t>
+          <t>cat__Pest_Rice Bug, Aphids, Stem Borer, None</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>5.159168116392555e-05</v>
+        <v>5.9612748504807e-05</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, None, Armyworm, Stem Borer</t>
+          <t>cat__Pest_None, Aphids, Armyworm, Stem Borer</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>5.121846580931133e-05</v>
+        <v>5.546959260121208e-05</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Aphids, Armyworm, Stem Borer</t>
+          <t>cat__Pest_Stem Borer, None, Aphids, Armyworm</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>4.971867174389377e-05</v>
+        <v>5.479785104221092e-05</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Aphids, Stem Borer, None</t>
+          <t>cat__Pest_Armyworm, Aphids, Rice Bug, None</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>4.9470862298246e-05</v>
+        <v>5.279049587246815e-05</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Aphids, Rice Bug, Armyworm</t>
+          <t>cat__Pest_Armyworm, Aphids, None, Rice Bug</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>4.846642349792685e-05</v>
+        <v>5.196767101931517e-05</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Aphids, None, Rice Bug</t>
+          <t>cat__Pest_None, Rice Bug, Armyworm, Stem Borer</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>4.753927415538055e-05</v>
+        <v>4.833624453377353e-05</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Armyworm, None, Rice Bug</t>
+          <t>cat__Pest_Aphids, Rice Bug, Stem Borer, None</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>4.706422405826766e-05</v>
+        <v>4.799174051086017e-05</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Stem Borer, None, Rice Bug</t>
+          <t>cat__Pest_Rice Bug, Aphids, None, Armyworm</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>4.635523387181221e-05</v>
+        <v>4.2015550165016e-05</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Aphids, None, Armyworm</t>
+          <t>cat__Pest_None, Armyworm, Stem Borer, Aphids</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>4.124582236980215e-05</v>
+        <v>4.12273191153619e-05</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Aphids, Armyworm, Rice Bug</t>
+          <t>cat__Pest_Armyworm, Aphids, Rice Bug, Stem Borer</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>4.069722708727879e-05</v>
+        <v>4.079374623400854e-05</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Rice Bug, None</t>
+          <t>cat__Pest_Armyworm, None, Aphids, Rice Bug</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>3.895977057616325e-05</v>
+        <v>3.949820824083374e-05</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Rice Bug, Stem Borer</t>
+          <t>cat__Pest_Stem Borer, Rice Bug, None</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>3.759795936191979e-05</v>
+        <v>3.842897496610587e-05</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Stem Borer, Armyworm</t>
+          <t>cat__Pest_None, Aphids, Stem Borer</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>3.738143750496642e-05</v>
+        <v>3.829316835335383e-05</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, None, Aphids, Rice Bug</t>
+          <t>cat__Pest_Rice Bug, None, Armyworm, Stem Borer</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>3.511430720453652e-05</v>
+        <v>3.220001103754393e-05</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Rice Bug, Aphids, Stem Borer</t>
+          <t>cat__Pest_Aphids, None, Armyworm, Rice Bug</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>3.426771692125027e-05</v>
+        <v>2.074362854657897e-05</v>
       </c>
     </row>
     <row r="197">
@@ -2385,67 +2385,47 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>3.278959430130549e-05</v>
+        <v>1.723821017957366e-05</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Stem Borer, Armyworm, Rice Bug</t>
+          <t>cat__Pest_Armyworm, Stem Borer, None, Rice Bug</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>2.998916815764454e-05</v>
+        <v>1.478916383543255e-05</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Aphids, Rice Bug, Stem Borer</t>
+          <t>cat__Pest_None, Stem Borer, Armyworm, Rice Bug</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>2.73148546038661e-05</v>
+        <v>1.289753131749621e-05</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Armyworm, Stem Borer, Aphids</t>
+          <t>cat__Pest_Aphids, Armyworm, Rice Bug</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>2.388705445313191e-05</v>
+        <v>1.251279268565747e-05</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Rice Bug, None</t>
+          <t>cat__Pest_None, Aphids, Armyworm, Rice Bug</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>2.151789207910455e-05</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>cat__Pest_Aphids, None, Armyworm, Rice Bug</t>
-        </is>
-      </c>
-      <c r="B202" t="n">
-        <v>1.671869182446355e-05</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>cat__Pest_Aphids, Armyworm, Rice Bug</t>
-        </is>
-      </c>
-      <c r="B203" t="n">
-        <v>1.122346288216362e-05</v>
+        <v>7.040808781941092e-06</v>
       </c>
     </row>
   </sheetData>

--- a/feature_importance.xlsx
+++ b/feature_importance.xlsx
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4805116906843864</v>
+        <v>0.4832528054571789</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2100756338383808</v>
+        <v>0.2084406137580051</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1211377286582241</v>
+        <v>0.1213141821382475</v>
       </c>
     </row>
     <row r="5">
@@ -465,27 +465,27 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08833365915606908</v>
+        <v>0.08733674649299959</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cat__Subsidy Type_Fertilizer Subsidy</t>
+          <t>cat__Subsidy Type_Seed Subsidy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008788344378516236</v>
+        <v>0.008761840132589989</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cat__Subsidy Type_Seed Subsidy</t>
+          <t>cat__Subsidy Type_Fertilizer Subsidy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008566712193584528</v>
+        <v>0.008574082546019546</v>
       </c>
     </row>
     <row r="8">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.004922302170144531</v>
+        <v>0.00513140524939445</v>
       </c>
     </row>
     <row r="9">
@@ -505,27 +505,27 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.004345509593143879</v>
+        <v>0.004352609143741624</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cat__Calamity_Landslide</t>
+          <t>cat__Calamity_nan</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.004209394641090301</v>
+        <v>0.004098844523579033</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cat__Calamity_nan</t>
+          <t>cat__Calamity_Landslide</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.004124239976009894</v>
+        <v>0.003953964334166088</v>
       </c>
     </row>
     <row r="12">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.00402099670284769</v>
+        <v>0.003631579884384044</v>
       </c>
     </row>
     <row r="13">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.002617168277394204</v>
+        <v>0.003222813595370344</v>
       </c>
     </row>
     <row r="14">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.002437304377061722</v>
+        <v>0.002619167969899692</v>
       </c>
     </row>
     <row r="15">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.002344776050269097</v>
+        <v>0.002348647685010789</v>
       </c>
     </row>
     <row r="16">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.002309293648155224</v>
+        <v>0.002335108390036128</v>
       </c>
     </row>
     <row r="17">
@@ -585,27 +585,27 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.002131089349005432</v>
+        <v>0.002102465440772183</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Aphids, Armyworm</t>
+          <t>cat__Pest_Armyworm, Aphids</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.001150691956473005</v>
+        <v>0.001190306223843554</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Aphids</t>
+          <t>cat__Pest_None, Aphids, Armyworm</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.00107365130561234</v>
+        <v>0.001058693090066841</v>
       </c>
     </row>
     <row r="20">
@@ -615,47 +615,47 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.001009655592825959</v>
+        <v>0.001020608265017611</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Stem Borer</t>
+          <t>cat__Pest_Stem Borer, Armyworm</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0009499167755686727</v>
+        <v>0.0008557342415559638</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Stem Borer</t>
+          <t>cat__Pest_None, Rice Bug</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.000910707865291501</v>
+        <v>0.0008413768619053574</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Rice Bug</t>
+          <t>cat__Pest_Armyworm, Stem Borer</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0008944729863254991</v>
+        <v>0.0008379329040191645</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Aphids</t>
+          <t>cat__Pest_None, Stem Borer</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0007657506189867166</v>
+        <v>0.0008379183606194648</v>
       </c>
     </row>
     <row r="25">
@@ -665,17 +665,17 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0007545469635960729</v>
+        <v>0.0007744868031055758</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Armyworm</t>
+          <t>cat__Pest_Rice Bug, Stem Borer, Aphids</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0007423822914979084</v>
+        <v>0.0007472508732799351</v>
       </c>
     </row>
     <row r="27">
@@ -685,17 +685,17 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0006684344979691162</v>
+        <v>0.0007310157747036501</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Rice Bug</t>
+          <t>cat__Pest_None, Aphids</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.000654964362791285</v>
+        <v>0.0007264478240978861</v>
       </c>
     </row>
     <row r="29">
@@ -705,47 +705,47 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0006417632333505735</v>
+        <v>0.0007201318825669384</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Rice Bug, Aphids</t>
+          <t>cat__Pest_Armyworm, None, Aphids</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0006261280462633315</v>
+        <v>0.0006301642121622541</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, None</t>
+          <t>cat__Pest_Aphids, Rice Bug</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0006254996983877137</v>
+        <v>0.0006278293670253085</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Stem Borer, Aphids</t>
+          <t>cat__Pest_Rice Bug, Aphids</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0006238064297569266</v>
+        <v>0.0005908120329355449</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, None, Aphids</t>
+          <t>cat__Pest_Stem Borer, None</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0006077681050146435</v>
+        <v>0.0005901900902286607</v>
       </c>
     </row>
     <row r="34">
@@ -755,27 +755,27 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0006006647024967024</v>
+        <v>0.0005779741790463998</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Aphids</t>
+          <t>cat__Pest_Stem Borer, Aphids</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0005946310952469303</v>
+        <v>0.000539746517447209</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Rice Bug, Aphids</t>
+          <t>cat__Pest_Rice Bug, Stem Borer</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.0005701972844577709</v>
+        <v>0.0005359213920984813</v>
       </c>
     </row>
     <row r="37">
@@ -785,77 +785,77 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.0005584501341871413</v>
+        <v>0.0005340283624844049</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Stem Borer</t>
+          <t>cat__Pest_Stem Borer, Rice Bug, Armyworm</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.0005578265055202013</v>
+        <v>0.0005274423338036928</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Aphids, None, Armyworm</t>
+          <t>cat__Pest_None, Rice Bug, Aphids</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.000545102129818794</v>
+        <v>0.0005219239433867784</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Stem Borer, Aphids, Armyworm</t>
+          <t>cat__Pest_Armyworm, Stem Borer, None</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.0005394469642423518</v>
+        <v>0.0005155130096560029</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, None</t>
+          <t>cat__Pest_Stem Borer, Rice Bug, Aphids</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.0005226550913302513</v>
+        <v>0.0005154238367803208</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Aphids</t>
+          <t>cat__Pest_None, Stem Borer, Aphids, Armyworm</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.0005196613035506297</v>
+        <v>0.0005062398283562218</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Armyworm</t>
+          <t>cat__Pest_Rice Bug, Stem Borer, None</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.0005178128081806994</v>
+        <v>0.0005048408311491719</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Stem Borer, None</t>
+          <t>cat__Pest_Rice Bug, None</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.0005002942615616993</v>
+        <v>0.0005033175267837606</v>
       </c>
     </row>
     <row r="45">
@@ -865,57 +865,57 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.0004982562499491243</v>
+        <v>0.0004923628339394638</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Rice Bug</t>
+          <t>cat__Pest_Armyworm, None</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.0004894122381780088</v>
+        <v>0.0004719116788398387</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Rice Bug, Aphids</t>
+          <t>cat__Pest_Rice Bug, Armyworm</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0004873120516893501</v>
+        <v>0.0004717272771460926</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Stem Borer, None</t>
+          <t>cat__Pest_Aphids, Rice Bug, Armyworm, Stem Borer</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0004861215838506107</v>
+        <v>0.0004643005103673878</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Rice Bug, Stem Borer, Aphids</t>
+          <t>cat__Pest_Armyworm, Rice Bug, Aphids</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0004837394934728605</v>
+        <v>0.0004430593864444522</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, None</t>
+          <t>cat__Pest_None, Armyworm</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.0004777800840643077</v>
+        <v>0.0004372159395571415</v>
       </c>
     </row>
     <row r="51">
@@ -925,57 +925,57 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0004682151818963718</v>
+        <v>0.0004316926962010478</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Rice Bug, Armyworm, Stem Borer</t>
+          <t>cat__Pest_None, Rice Bug, Stem Borer</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.0004670305423314676</v>
+        <v>0.0004295152610447904</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Rice Bug, Armyworm</t>
+          <t>cat__Pest_Stem Borer, Rice Bug</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.0004525837006957452</v>
+        <v>0.0004272442515815059</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Armyworm</t>
+          <t>cat__Pest_Stem Borer, None, Rice Bug</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.000447281996261914</v>
+        <v>0.0004233869964302567</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, None, Rice Bug</t>
+          <t>cat__Pest_None, Armyworm, Rice Bug</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.0004460106840673973</v>
+        <v>0.000413050384115574</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Aphids, Armyworm, Rice Bug</t>
+          <t>cat__Pest_Stem Borer, Aphids, None, Armyworm</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.0004448300622060463</v>
+        <v>0.0004111088020921679</v>
       </c>
     </row>
     <row r="57">
@@ -985,107 +985,107 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.00043882261306085</v>
+        <v>0.0004008833629443766</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Aphids, Stem Borer</t>
+          <t>cat__Pest_Armyworm, Rice Bug, Stem Borer, Aphids</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.0004092628940832721</v>
+        <v>0.0003961568199749677</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, None, Armyworm</t>
+          <t>cat__Pest_Stem Borer, Aphids, None</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.0003968729945482105</v>
+        <v>0.0003723934020158231</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, None, Armyworm, Aphids</t>
+          <t>cat__Pest_Rice Bug, Aphids, Stem Borer</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.0003890412377943569</v>
+        <v>0.0003691003495840169</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, None, Stem Borer, Armyworm</t>
+          <t>cat__Pest_Stem Borer, Aphids, Armyworm, Rice Bug</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.0003842285607024329</v>
+        <v>0.0003635597891339906</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Rice Bug, Armyworm, Aphids</t>
+          <t>cat__Pest_Rice Bug, None, Armyworm, Aphids</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.0003684005006426449</v>
+        <v>0.0003626621177235625</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Aphids, None</t>
+          <t>cat__Pest_Stem Borer, None, Armyworm, Aphids</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.0003654787852390656</v>
+        <v>0.000360151185947202</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, None, Armyworm, Aphids</t>
+          <t>cat__Pest_Aphids, None, Armyworm</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.0003612062161029999</v>
+        <v>0.000359571819575506</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Armyworm, Rice Bug</t>
+          <t>cat__Pest_Stem Borer, Armyworm, None</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.0003564921864098944</v>
+        <v>0.0003536393251165595</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, None, Armyworm</t>
+          <t>cat__Pest_Aphids, None, Stem Borer, Armyworm</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.0003563367274118559</v>
+        <v>0.0003459439256910724</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Stem Borer, Rice Bug, Armyworm</t>
+          <t>cat__Pest_Stem Borer, Rice Bug, Armyworm, Aphids</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.0003561943555110225</v>
+        <v>0.0003377610408756131</v>
       </c>
     </row>
     <row r="68">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.0003523794500160261</v>
+        <v>0.0003365064642480842</v>
       </c>
     </row>
     <row r="69">
@@ -1105,27 +1105,27 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.0003496970062328566</v>
+        <v>0.0003345805566991854</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Armyworm, None</t>
+          <t>cat__Pest_Stem Borer, None, Armyworm</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.000349690328765611</v>
+        <v>0.0003295410199238149</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, None, Aphids</t>
+          <t>cat__Pest_None, Aphids, Rice Bug, Stem Borer</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.000341105891067886</v>
+        <v>0.0003207500918919533</v>
       </c>
     </row>
     <row r="72">
@@ -1135,37 +1135,37 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.0003375572106865224</v>
+        <v>0.0003203326029576875</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Stem Borer, Aphids</t>
+          <t>cat__Pest_Aphids, Stem Borer, Rice Bug, Armyworm</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.0003188500775780332</v>
+        <v>0.0003041594813943286</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Aphids, Rice Bug, Stem Borer</t>
+          <t>cat__Pest_Aphids, Rice Bug, None</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.0003120206857519895</v>
+        <v>0.0002904760393999706</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Rice Bug, None</t>
+          <t>cat__Pest_None, Rice Bug, Armyworm</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.0003115471533905401</v>
+        <v>0.0002843381746288678</v>
       </c>
     </row>
     <row r="76">
@@ -1175,1027 +1175,1027 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.0003013851287291981</v>
+        <v>0.0002817920402301921</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Rice Bug, Stem Borer</t>
+          <t>cat__Pest_Aphids, Armyworm, None</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.0002943317650454535</v>
+        <v>0.0002708931907045115</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, None, Aphids, Stem Borer</t>
+          <t>cat__Pest_Rice Bug, None, Aphids, Stem Borer</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.0002903763722945483</v>
+        <v>0.0002699406872624254</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Armyworm, Aphids, Stem Borer</t>
+          <t>cat__Pest_Rice Bug, None, Aphids</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.0002897435632609095</v>
+        <v>0.000269250075231451</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Armyworm, Aphids, Rice Bug</t>
+          <t>cat__Pest_None, Aphids, Rice Bug</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.0002773274613002487</v>
+        <v>0.0002661727097687337</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, None, Rice Bug, Armyworm</t>
+          <t>cat__Pest_None, Armyworm, Aphids, Rice Bug</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.0002658374611094291</v>
+        <v>0.0002659614490532286</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Aphids, Rice Bug</t>
+          <t>cat__Pest_Stem Borer, Aphids, Armyworm, None</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.0002636801745246313</v>
+        <v>0.0002653662089462962</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, None, Rice Bug</t>
+          <t>cat__Pest_Rice Bug, Armyworm, None</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.000261163052070872</v>
+        <v>0.0002639481228511497</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Rice Bug, Armyworm, Aphids</t>
+          <t>cat__Pest_Armyworm, Stem Borer, Aphids, Rice Bug</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.0002541817088313096</v>
+        <v>0.0002628533139053537</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, None, Rice Bug, Aphids</t>
+          <t>cat__Pest_Rice Bug, Armyworm, Aphids, Stem Borer</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.0002533458561269561</v>
+        <v>0.0002582701592381591</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, None, Aphids, Stem Borer</t>
+          <t>cat__Pest_Stem Borer, Aphids, Rice Bug, None</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.0002524783877316037</v>
+        <v>0.0002561686605364453</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Armyworm, Stem Borer, Aphids</t>
+          <t>cat__Pest_None, Armyworm, Aphids</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.0002523613018491513</v>
+        <v>0.0002531144009952778</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Rice Bug, Armyworm</t>
+          <t>cat__Pest_None, Rice Bug, Armyworm, Aphids</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.0002509545064879312</v>
+        <v>0.0002509239417403915</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Armyworm, Aphids, Stem Borer</t>
+          <t>cat__Pest_Armyworm, None, Rice Bug</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.0002480121746178102</v>
+        <v>0.0002488856064783388</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Armyworm, Stem Borer</t>
+          <t>cat__Pest_None, Armyworm, Aphids, Stem Borer</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.0002475997504171111</v>
+        <v>0.000245651717315663</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Aphids, Armyworm, None</t>
+          <t>cat__Pest_Armyworm, None, Rice Bug, Aphids</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.0002418108855394456</v>
+        <v>0.0002357899081461689</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Aphids, Rice Bug</t>
+          <t>cat__Pest_Rice Bug, Stem Borer, None, Aphids</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.0002237601373581382</v>
+        <v>0.0002335180688979585</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Armyworm, Aphids, None</t>
+          <t>cat__Pest_Armyworm, Stem Borer, Aphids</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.0002214886926846076</v>
+        <v>0.000225114630458703</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Aphids, Armyworm, Stem Borer</t>
+          <t>cat__Pest_Armyworm, None, Rice Bug, Stem Borer</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.0002213372218752584</v>
+        <v>0.0002235977078131355</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Armyworm, None</t>
+          <t>cat__Pest_Armyworm, None, Aphids, Stem Borer</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.0002205829819757469</v>
+        <v>0.0002232146647761357</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Armyworm, None</t>
+          <t>cat__Pest_Armyworm, Rice Bug, Stem Borer, None</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.0002193812515700006</v>
+        <v>0.000221545747600291</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, None, Rice Bug, Stem Borer</t>
+          <t>cat__Pest_Armyworm, Rice Bug, Stem Borer</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.0002187630488862446</v>
+        <v>0.0002209326085022209</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Armyworm, Aphids</t>
+          <t>cat__Pest_None, Armyworm, Stem Borer</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.0002172037994953463</v>
+        <v>0.0002184434876441958</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Rice Bug, None, Aphids</t>
+          <t>cat__Pest_Stem Borer, None, Rice Bug, Armyworm</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.0002171927084479166</v>
+        <v>0.000215063942637589</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Stem Borer, None, Aphids</t>
+          <t>cat__Pest_Rice Bug, Stem Borer, Aphids, None</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.0002147763624261813</v>
+        <v>0.0002137382127104659</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Stem Borer, Aphids, None</t>
+          <t>cat__Pest_Rice Bug, Armyworm, Stem Borer, Aphids</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.0002047324313157798</v>
+        <v>0.0002111401902885112</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Stem Borer, Aphids, Armyworm</t>
+          <t>cat__Pest_Rice Bug, Armyworm, Aphids</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.0001974288101481214</v>
+        <v>0.0002087832230700329</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, None, Stem Borer</t>
+          <t>cat__Pest_Stem Borer, Aphids, Rice Bug</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.000197353663189612</v>
+        <v>0.0002075253754083766</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Stem Borer, None, Rice Bug</t>
+          <t>cat__Pest_Aphids, None, Stem Borer</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.0001970997811763822</v>
+        <v>0.000205496848656001</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Armyworm, Aphids</t>
+          <t>cat__Pest_Stem Borer, Rice Bug, None, Aphids</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.0001951179382496954</v>
+        <v>0.0002045241822413659</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Stem Borer, Aphids, None</t>
+          <t>cat__Pest_Aphids, Stem Borer, None, Rice Bug</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.0001934195534506383</v>
+        <v>0.0002027108025240586</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Rice Bug, Armyworm</t>
+          <t>cat__Pest_Stem Borer, Armyworm, Aphids</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.0001929199515798703</v>
+        <v>0.0002008985075407353</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, None, Rice Bug, Armyworm</t>
+          <t>cat__Pest_Rice Bug, Aphids, Armyworm, Stem Borer</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.0001928833333717703</v>
+        <v>0.0001977656318203112</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Armyworm, Stem Borer, None</t>
+          <t>cat__Pest_Rice Bug, Stem Borer, Armyworm, Aphids</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.0001923361872256562</v>
+        <v>0.0001977376568641774</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Armyworm, Rice Bug, Aphids</t>
+          <t>cat__Pest_Stem Borer, Armyworm, Aphids, None</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.0001922282956753472</v>
+        <v>0.0001947718636178344</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Armyworm, Rice Bug, Aphids</t>
+          <t>cat__Pest_Stem Borer, Armyworm, Rice Bug, Aphids</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.0001917712659213094</v>
+        <v>0.0001913965064429488</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Stem Borer, Armyworm, Aphids</t>
+          <t>cat__Pest_Stem Borer, Aphids, Armyworm</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.0001908994921688251</v>
+        <v>0.000190218151051319</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Aphids, Rice Bug, None</t>
+          <t>cat__Pest_Rice Bug, None, Stem Borer, Aphids</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.0001899192797592899</v>
+        <v>0.0001885742113243231</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Aphids, Stem Borer, Armyworm</t>
+          <t>cat__Pest_Aphids, Armyworm, None, Stem Borer</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.0001889780616079894</v>
+        <v>0.0001862646579393455</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Stem Borer, None</t>
+          <t>cat__Pest_Aphids, Armyworm, Stem Borer, None</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.0001883085342605044</v>
+        <v>0.0001861954817610514</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Armyworm, Aphids</t>
+          <t>cat__Pest_Rice Bug, Aphids, Armyworm, None</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.0001829820343587248</v>
+        <v>0.0001848492969503456</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Aphids, Armyworm, None</t>
+          <t>cat__Pest_Rice Bug, Aphids, Stem Borer, Armyworm</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.0001820311744243865</v>
+        <v>0.0001838747132650148</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Rice Bug, None, Stem Borer</t>
+          <t>cat__Pest_Aphids, None, Rice Bug, Armyworm</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.0001752717628656713</v>
+        <v>0.0001822885902483193</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Aphids, Stem Borer, Armyworm</t>
+          <t>cat__Pest_None, Aphids, Stem Borer, Armyworm</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.0001717609002568438</v>
+        <v>0.0001810165706243548</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Aphids, Rice Bug, Armyworm</t>
+          <t>cat__Pest_Aphids, Stem Borer, None</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.0001698110023169601</v>
+        <v>0.0001797058715202418</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, None, Armyworm</t>
+          <t>cat__Pest_Aphids, Armyworm, Rice Bug, None</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.0001675690126288744</v>
+        <v>0.0001795499748524682</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, None, Stem Borer, Aphids</t>
+          <t>cat__Pest_Rice Bug, Stem Borer, Armyworm</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.0001655400804360697</v>
+        <v>0.0001794340512882595</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Stem Borer, Armyworm</t>
+          <t>cat__Pest_None, Stem Borer, Rice Bug</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.0001651886266716899</v>
+        <v>0.000175929710124344</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Aphids, Armyworm</t>
+          <t>cat__Pest_Stem Borer, Aphids, Rice Bug, Armyworm</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.0001648301158976988</v>
+        <v>0.0001748829435027007</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Rice Bug, Stem Borer</t>
+          <t>cat__Pest_Rice Bug, Stem Borer, Aphids, Armyworm</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.0001627807390064265</v>
+        <v>0.000174533508455157</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Rice Bug, Aphids, Armyworm</t>
+          <t>cat__Pest_Rice Bug, None, Armyworm</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.00016160595103038</v>
+        <v>0.000169286289314072</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Rice Bug, None, Armyworm</t>
+          <t>cat__Pest_Rice Bug, None, Stem Borer</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.0001608289505770041</v>
+        <v>0.0001669155099932552</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Stem Borer, Rice Bug, None</t>
+          <t>cat__Pest_None, Armyworm, Rice Bug, Aphids</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.0001604880965102918</v>
+        <v>0.0001564019236430407</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Stem Borer, Rice Bug, Aphids</t>
+          <t>cat__Pest_Armyworm, Aphids, Stem Borer, Rice Bug</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.0001591669670442723</v>
+        <v>0.0001538092248851452</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Aphids, Stem Borer, Rice Bug</t>
+          <t>cat__Pest_Aphids, Rice Bug, Stem Borer</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.0001561218086078456</v>
+        <v>0.0001531262258051033</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Aphids, Stem Borer</t>
+          <t>cat__Pest_None, Aphids, Armyworm, Stem Borer</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.0001538458740797217</v>
+        <v>0.0001519134922730626</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, None, Rice Bug, Stem Borer</t>
+          <t>cat__Pest_Aphids, Rice Bug, None, Armyworm</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.0001483435261574543</v>
+        <v>0.0001508368027556765</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Armyworm, Rice Bug, None</t>
+          <t>cat__Pest_Armyworm, Stem Borer, Aphids, None</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.0001429369242851029</v>
+        <v>0.000146620918524487</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Aphids, Rice Bug</t>
+          <t>cat__Pest_Stem Borer, None, Armyworm, Rice Bug</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.0001425223458217002</v>
+        <v>0.0001431993291016232</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Rice Bug, None, Stem Borer</t>
+          <t>cat__Pest_Armyworm, Stem Borer, Rice Bug, None</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.000141095589784364</v>
+        <v>0.0001421990227026816</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Stem Borer, Armyworm, Aphids</t>
+          <t>cat__Pest_Armyworm, Aphids, Stem Borer</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.0001387081779614268</v>
+        <v>0.0001415307023379378</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Armyworm, Stem Borer</t>
+          <t>cat__Pest_Aphids, Rice Bug, None, Stem Borer</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.0001375123984221588</v>
+        <v>0.0001410995765567006</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Rice Bug, Stem Borer, Armyworm</t>
+          <t>cat__Pest_Stem Borer, Rice Bug, Aphids, Armyworm</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.0001355832943936967</v>
+        <v>0.0001405423308297559</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Stem Borer, Rice Bug, None</t>
+          <t>cat__Pest_None, Stem Borer, Rice Bug, Armyworm</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.0001333250439148797</v>
+        <v>0.0001402556943290781</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Rice Bug, Stem Borer, None</t>
+          <t>cat__Pest_Aphids, Stem Borer, Rice Bug, None</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.0001310943583341602</v>
+        <v>0.0001383330948245554</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Stem Borer, Aphids, Rice Bug</t>
+          <t>cat__Pest_Stem Borer, Armyworm, Rice Bug, None</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.0001303974495134227</v>
+        <v>0.0001378865450796892</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Stem Borer, Rice Bug, Armyworm</t>
+          <t>cat__Pest_Stem Borer, Armyworm, Rice Bug</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.0001268615765672975</v>
+        <v>0.0001358396502460115</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Armyworm, Aphids, None</t>
+          <t>cat__Pest_Armyworm, Rice Bug, None, Aphids</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.0001259602795441273</v>
+        <v>0.0001340194316533798</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Armyworm, Rice Bug</t>
+          <t>cat__Pest_Aphids, Rice Bug, Armyworm</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.0001255331326133995</v>
+        <v>0.000132601282963487</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, None, Stem Borer</t>
+          <t>cat__Pest_Armyworm, Stem Borer, Rice Bug, Aphids</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.0001255216817387752</v>
+        <v>0.0001322636676038598</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Rice Bug, None, Aphids</t>
+          <t>cat__Pest_Armyworm, Rice Bug, None, Stem Borer</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.0001248793998876363</v>
+        <v>0.0001305961575706982</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Stem Borer, Aphids</t>
+          <t>cat__Pest_Aphids, Rice Bug, Armyworm, None</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.0001245973891270837</v>
+        <v>0.0001304087538696728</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, None, Armyworm, Rice Bug</t>
+          <t>cat__Pest_Rice Bug, Armyworm, Aphids, None</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.0001243606001851617</v>
+        <v>0.0001276954397418789</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, None, Rice Bug, Aphids</t>
+          <t>cat__Pest_Armyworm, Aphids, None, Stem Borer</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.000117208290348342</v>
+        <v>0.0001264364990180521</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Armyworm, None, Rice Bug</t>
+          <t>cat__Pest_None, Stem Borer, Armyworm, Aphids</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.00011617643610334</v>
+        <v>0.0001210899672190701</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Aphids, None, Stem Borer</t>
+          <t>cat__Pest_Armyworm, Aphids, Rice Bug</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.0001158112947380661</v>
+        <v>0.0001168843132755982</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, None, Rice Bug</t>
+          <t>cat__Pest_None, Rice Bug, Stem Borer, Armyworm</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.0001157259618295161</v>
+        <v>0.0001136280477750784</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Rice Bug, Armyworm, None</t>
+          <t>cat__Pest_Rice Bug, Armyworm, None, Aphids</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.0001155304594855683</v>
+        <v>0.0001134483953840897</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Aphids, Stem Borer, Rice Bug</t>
+          <t>cat__Pest_Aphids, Armyworm, Stem Borer</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.0001134597855428206</v>
+        <v>0.0001109112075932176</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Stem Borer, None, Aphids</t>
+          <t>cat__Pest_Stem Borer, None, Aphids, Rice Bug</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.0001121313200143646</v>
+        <v>0.0001100559893054709</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Armyworm, None, Aphids</t>
+          <t>cat__Pest_Armyworm, None, Stem Borer, Aphids</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.0001097388577497324</v>
+        <v>0.000108768266986528</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, None, Stem Borer, Aphids</t>
+          <t>cat__Pest_Armyworm, Stem Borer, None, Aphids</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.0001080523225766881</v>
+        <v>0.000108386692654474</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, None, Stem Borer, Rice Bug</t>
+          <t>cat__Pest_None, Stem Borer, Aphids</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.0001077887248452694</v>
+        <v>0.0001083230046463771</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Armyworm, None, Stem Borer</t>
+          <t>cat__Pest_Aphids, None, Rice Bug, Stem Borer</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.0001077117599158344</v>
+        <v>0.0001077678614503555</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, None, Aphids, Rice Bug</t>
+          <t>cat__Pest_None, Rice Bug, Aphids, Stem Borer</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.0001062261691351597</v>
+        <v>0.0001056740243265932</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Rice Bug, Stem Borer</t>
+          <t>cat__Pest_Aphids, None, Rice Bug</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.00010521646772756</v>
+        <v>0.0001021713082565803</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Rice Bug, None, Armyworm</t>
+          <t>cat__Pest_Aphids, None, Stem Borer, Rice Bug</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.0001049617757724417</v>
+        <v>9.746149392979138e-05</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Stem Borer, Aphids, Rice Bug</t>
+          <t>cat__Pest_Stem Borer, None, Rice Bug, Aphids</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.0001035576041427578</v>
+        <v>9.687669363171367e-05</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Armyworm, None, Aphids</t>
+          <t>cat__Pest_Aphids, Rice Bug, Stem Borer, Armyworm</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.0001005113245236022</v>
+        <v>9.445877380403636e-05</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Armyworm, Stem Borer, None</t>
+          <t>cat__Pest_None, Aphids, Stem Borer, Rice Bug</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>9.916705069585192e-05</v>
+        <v>9.366406335614382e-05</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Rice Bug, Stem Borer, Armyworm</t>
+          <t>cat__Pest_Aphids, Stem Borer, None, Armyworm</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>9.655264913422166e-05</v>
+        <v>9.294645326508984e-05</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Rice Bug, Aphids, Stem Borer</t>
+          <t>cat__Pest_Rice Bug, Armyworm, None, Stem Borer</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>9.41770408886878e-05</v>
+        <v>9.2676666419912e-05</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Stem Borer, None, Armyworm</t>
+          <t>cat__Pest_None, Aphids, Rice Bug, Armyworm</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>9.196436966987092e-05</v>
+        <v>9.133142527797103e-05</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Aphids, Rice Bug, Armyworm</t>
+          <t>cat__Pest_Stem Borer, Armyworm, None, Rice Bug</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>8.960792534842458e-05</v>
+        <v>8.990175766066438e-05</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Stem Borer, None, Armyworm</t>
+          <t>cat__Pest_Rice Bug, Armyworm, Stem Borer, None</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>8.701096793328094e-05</v>
+        <v>8.882112739789973e-05</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Rice Bug, Aphids, Stem Borer</t>
+          <t>cat__Pest_Stem Borer, Armyworm, None, Aphids</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>8.556362112904411e-05</v>
+        <v>8.870084791435394e-05</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Stem Borer, Rice Bug</t>
+          <t>cat__Pest_None, Armyworm, Rice Bug, Stem Borer</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>8.41324580573003e-05</v>
+        <v>8.619272068077826e-05</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Stem Borer, Rice Bug</t>
+          <t>cat__Pest_None, Stem Borer, Aphids, Rice Bug</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>8.167752689958161e-05</v>
+        <v>8.41583356004382e-05</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Armyworm, Rice Bug, Stem Borer</t>
+          <t>cat__Pest_Armyworm, Rice Bug, Aphids, Stem Borer</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>7.931410296825779e-05</v>
+        <v>8.328671193225881e-05</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Stem Borer, Armyworm, None</t>
+          <t>cat__Pest_Rice Bug, Stem Borer, None, Armyworm</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>7.526159766431289e-05</v>
+        <v>7.901214417912385e-05</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Armyworm, None, Stem Borer</t>
+          <t>cat__Pest_Aphids, Stem Borer, Rice Bug</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>7.275352732577198e-05</v>
+        <v>7.48332481385545e-05</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Rice Bug, None</t>
+          <t>cat__Pest_Stem Borer, Rice Bug, None, Armyworm</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>6.889933955715963e-05</v>
+        <v>7.479002872539165e-05</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Armyworm, None, Rice Bug</t>
+          <t>cat__Pest_Rice Bug, Aphids, Stem Borer, None</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>6.825970296698002e-05</v>
+        <v>7.390312048820795e-05</v>
       </c>
     </row>
     <row r="179">
@@ -2205,17 +2205,17 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>6.419514303421773e-05</v>
+        <v>7.234310617543164e-05</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Armyworm, Rice Bug, None</t>
+          <t>cat__Pest_Aphids, Armyworm, None, Rice Bug</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>6.218215208331202e-05</v>
+        <v>7.197678019089171e-05</v>
       </c>
     </row>
     <row r="181">
@@ -2225,67 +2225,67 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>6.081276568075594e-05</v>
+        <v>6.858384491208179e-05</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Aphids, Stem Borer, None</t>
+          <t>cat__Pest_Stem Borer, None, Aphids, Armyworm</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>5.9612748504807e-05</v>
+        <v>6.297558045523109e-05</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Aphids, Armyworm, Stem Borer</t>
+          <t>cat__Pest_Armyworm, Aphids, Rice Bug, Stem Borer</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>5.546959260121208e-05</v>
+        <v>5.939513575636178e-05</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, None, Aphids, Armyworm</t>
+          <t>cat__Pest_Rice Bug, Stem Borer, Armyworm, None</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>5.479785104221092e-05</v>
+        <v>5.765361495476963e-05</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Aphids, Rice Bug, None</t>
+          <t>cat__Pest_None, Rice Bug, Armyworm, Stem Borer</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>5.279049587246815e-05</v>
+        <v>5.675239268536738e-05</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Aphids, None, Rice Bug</t>
+          <t>cat__Pest_Armyworm, Aphids, Rice Bug, None</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>5.196767101931517e-05</v>
+        <v>5.171179588683595e-05</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Rice Bug, Armyworm, Stem Borer</t>
+          <t>cat__Pest_Armyworm, Aphids, None, Rice Bug</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>4.833624453377353e-05</v>
+        <v>4.964715941504807e-05</v>
       </c>
     </row>
     <row r="188">
@@ -2295,67 +2295,67 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>4.799174051086017e-05</v>
+        <v>4.903486127451888e-05</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Bug, Aphids, None, Armyworm</t>
+          <t>cat__Pest_None, Armyworm, Stem Borer, Aphids</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>4.2015550165016e-05</v>
+        <v>4.409187725527182e-05</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Armyworm, Stem Borer, Aphids</t>
+          <t>cat__Pest_Armyworm, Rice Bug, None</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>4.12273191153619e-05</v>
+        <v>4.34542557552284e-05</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, Aphids, Rice Bug, Stem Borer</t>
+          <t>cat__Pest_Stem Borer, Rice Bug, None</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>4.079374623400854e-05</v>
+        <v>4.267869256023824e-05</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>cat__Pest_Armyworm, None, Aphids, Rice Bug</t>
+          <t>cat__Pest_None, Aphids, Stem Borer</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>3.949820824083374e-05</v>
+        <v>4.130317956117786e-05</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>cat__Pest_Stem Borer, Rice Bug, None</t>
+          <t>cat__Pest_Rice Bug, Aphids, None, Armyworm</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>3.842897496610587e-05</v>
+        <v>3.350731597824361e-05</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Aphids, Stem Borer</t>
+          <t>cat__Pest_Armyworm, None, Aphids, Rice Bug</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>3.829316835335383e-05</v>
+        <v>3.030480198966356e-05</v>
       </c>
     </row>
     <row r="195">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>3.220001103754393e-05</v>
+        <v>2.204879606626298e-05</v>
       </c>
     </row>
     <row r="196">
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>2.074362854657897e-05</v>
+        <v>1.652984956310177e-05</v>
       </c>
     </row>
     <row r="197">
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>1.723821017957366e-05</v>
+        <v>1.476266211307422e-05</v>
       </c>
     </row>
     <row r="198">
@@ -2395,27 +2395,27 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>1.478916383543255e-05</v>
+        <v>1.392587751563178e-05</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>cat__Pest_None, Stem Borer, Armyworm, Rice Bug</t>
+          <t>cat__Pest_Aphids, Armyworm, Rice Bug</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>1.289753131749621e-05</v>
+        <v>1.347348215754138e-05</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>cat__Pest_Aphids, Armyworm, Rice Bug</t>
+          <t>cat__Pest_None, Stem Borer, Armyworm, Rice Bug</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>1.251279268565747e-05</v>
+        <v>1.254925743440588e-05</v>
       </c>
     </row>
     <row r="201">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>7.040808781941092e-06</v>
+        <v>7.902741611531539e-06</v>
       </c>
     </row>
   </sheetData>

--- a/feature_importance.xlsx
+++ b/feature_importance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,151 +431,151 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>num__Crop Yield After (tons)</t>
+          <t>num__Feedback Score</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4300088442445871</v>
+        <v>0.4805116906843864</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>num__Feedback Score</t>
+          <t>num__Crop Yield After</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4283588317646329</v>
+        <v>0.2100756338383808</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>num__Farm Size (ha)</t>
+          <t>num__Crop Yield Before</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07083842806183634</v>
+        <v>0.1211377286582241</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>num__Crop Yield Before (tons)</t>
+          <t>num__Farm Size (ha)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02569810591481089</v>
+        <v>0.08833365915606908</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cat__Pest_Golden Apple Snail</t>
+          <t>cat__Subsidy Type_Fertilizer Subsidy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003211023396894278</v>
+        <v>0.008788344378516236</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Stem Borer</t>
+          <t>cat__Subsidy Type_Seed Subsidy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003082324967542704</v>
+        <v>0.008566712193584528</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cat__Pest_Rice Leaf Folder</t>
+          <t>cat__Calamity_Flood</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003016303058549174</v>
+        <v>0.004922302170144531</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cat__Calamity_Drought</t>
+          <t>cat__Calamity_Typhoon</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002985691417245799</v>
+        <v>0.004345509593143879</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cat__Pest_Brown Planthopper</t>
+          <t>cat__Calamity_Landslide</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.002926117147041132</v>
+        <v>0.004209394641090301</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cat__Calamity_Strong Winds</t>
+          <t>cat__Calamity_nan</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.002818420724878202</v>
+        <v>0.004124239976009894</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cat__Calamity_Landslide</t>
+          <t>cat__Calamity_Drought</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.002755143173132369</v>
+        <v>0.00402099670284769</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cat__Calamity_nan</t>
+          <t>cat__Pest_Aphids</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.002660822842853028</v>
+        <v>0.002617168277394204</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cat__Outcome Cause_Pest + Calamity</t>
+          <t>cat__Pest_Armyworm</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.002651526422761774</v>
+        <v>0.002437304377061722</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cat__Calamity_Heavy Rainfall</t>
+          <t>cat__Pest_Rice Bug</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.002638532333998378</v>
+        <v>0.002344776050269097</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cat__Calamity_Flood</t>
+          <t>cat__Pest_Stem Borer</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.002620629000762848</v>
+        <v>0.002309293648155224</v>
       </c>
     </row>
     <row r="17">
@@ -585,67 +585,1847 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.00257854572537562</v>
+        <v>0.002131089349005432</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cat__Calamity_Typhoon</t>
+          <t>cat__Pest_None, Aphids, Armyworm</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.002277676586099357</v>
+        <v>0.001150691956473005</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cat__Outcome Cause_Normal</t>
+          <t>cat__Pest_Armyworm, Aphids</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.002268013214815846</v>
+        <v>0.00107365130561234</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cat__Outcome Cause_Calamity</t>
+          <t>cat__Pest_Armyworm, Rice Bug</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.002235546260368905</v>
+        <v>0.001009655592825959</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cat__Calamity_Hailstorm</t>
+          <t>cat__Pest_Armyworm, Stem Borer</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.002190448440972047</v>
+        <v>0.0009499167755686727</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cat__Outcome Cause_Pest</t>
+          <t>cat__Pest_None, Stem Borer</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.002179025300841346</v>
+        <v>0.000910707865291501</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cat__Subsidy Type_Rice/Palay</t>
+          <t>cat__Pest_None, Rice Bug</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>0.0008944729863254991</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Aphids</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.0007657506189867166</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Armyworm</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.0007545469635960729</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Armyworm</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.0007423822914979084</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, None</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.0006684344979691162</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.000654964362791285</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.0006417632333505735</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Rice Bug, Aphids</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.0006261280462633315</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, None</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.0006254996983877137</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Stem Borer, Aphids</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.0006238064297569266</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, None, Aphids</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.0006077681050146435</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, None, Aphids</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.0006006647024967024</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Aphids</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.0005946310952469303</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Rice Bug, Aphids</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.0005701972844577709</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Stem Borer, Armyworm</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.0005584501341871413</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.0005578265055202013</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Aphids, None, Armyworm</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.000545102129818794</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Stem Borer, Aphids, Armyworm</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.0005394469642423518</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, None</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.0005226550913302513</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Aphids</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.0005196613035506297</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Armyworm</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.0005178128081806994</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Stem Borer, None</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.0005002942615616993</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Armyworm, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.0004982562499491243</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.0004894122381780088</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Rice Bug, Aphids</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.0004873120516893501</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Stem Borer, None</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.0004861215838506107</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Rice Bug, Stem Borer, Aphids</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.0004837394934728605</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, None</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.0004777800840643077</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Stem Borer, Armyworm, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.0004682151818963718</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Rice Bug, Armyworm, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.0004670305423314676</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Rice Bug, Armyworm</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.0004525837006957452</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Armyworm</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.000447281996261914</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, None, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.0004460106840673973</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Aphids, Armyworm, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.0004448300622060463</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Aphids, None</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0.00043882261306085</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Aphids, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.0004092628940832721</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, None, Armyworm</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0.0003968729945482105</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, None, Armyworm, Aphids</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0.0003890412377943569</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, None, Stem Borer, Armyworm</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0.0003842285607024329</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Rice Bug, Armyworm, Aphids</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0.0003684005006426449</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Aphids, None</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0.0003654787852390656</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, None, Armyworm, Aphids</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0.0003612062161029999</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Armyworm, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0.0003564921864098944</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, None, Armyworm</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0.0003563367274118559</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Stem Borer, Rice Bug, Armyworm</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.0003561943555110225</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Rice Bug, Aphids, Armyworm</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0.0003523794500160261</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Rice Bug, Armyworm, None</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0.0003496970062328566</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Armyworm, None</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.000349690328765611</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, None, Aphids</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.000341105891067886</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Aphids, Armyworm</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.0003375572106865224</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Stem Borer, Aphids</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0.0003188500775780332</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Aphids, Rice Bug, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0.0003120206857519895</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Rice Bug, None</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0.0003115471533905401</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, None, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.0003013851287291981</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Rice Bug, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0.0002943317650454535</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, None, Aphids, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0.0002903763722945483</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Armyworm, Aphids, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.0002897435632609095</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Armyworm, Aphids, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0.0002773274613002487</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, None, Rice Bug, Armyworm</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.0002658374611094291</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Aphids, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0.0002636801745246313</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, None, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0.000261163052070872</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Rice Bug, Armyworm, Aphids</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0.0002541817088313096</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, None, Rice Bug, Aphids</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0.0002533458561269561</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, None, Aphids, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0.0002524783877316037</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Armyworm, Stem Borer, Aphids</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0.0002523613018491513</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Rice Bug, Armyworm</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0.0002509545064879312</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Armyworm, Aphids, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0.0002480121746178102</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Armyworm, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0.0002475997504171111</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Aphids, Armyworm, None</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0.0002418108855394456</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Aphids, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0.0002237601373581382</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Armyworm, Aphids, None</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>0.0002214886926846076</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Aphids, Armyworm, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0.0002213372218752584</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Armyworm, None</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0.0002205829819757469</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Armyworm, None</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0.0002193812515700006</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, None, Rice Bug, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>0.0002187630488862446</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Armyworm, Aphids</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0.0002172037994953463</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Rice Bug, None, Aphids</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0.0002171927084479166</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Stem Borer, None, Aphids</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0.0002147763624261813</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Stem Borer, Aphids, None</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>0.0002047324313157798</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Stem Borer, Aphids, Armyworm</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>0.0001974288101481214</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, None, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>0.000197353663189612</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Stem Borer, None, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>0.0001970997811763822</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Armyworm, Aphids</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>0.0001951179382496954</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Stem Borer, Aphids, None</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>0.0001934195534506383</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Rice Bug, Armyworm</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>0.0001929199515798703</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, None, Rice Bug, Armyworm</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>0.0001928833333717703</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Armyworm, Stem Borer, None</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>0.0001923361872256562</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Armyworm, Rice Bug, Aphids</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>0.0001922282956753472</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Armyworm, Rice Bug, Aphids</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0.0001917712659213094</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Stem Borer, Armyworm, Aphids</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0.0001908994921688251</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Aphids, Rice Bug, None</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0.0001899192797592899</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Aphids, Stem Borer, Armyworm</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0.0001889780616079894</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Stem Borer, None</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>0.0001883085342605044</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Armyworm, Aphids</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0.0001829820343587248</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Aphids, Armyworm, None</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>0.0001820311744243865</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Rice Bug, None, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>0.0001752717628656713</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Aphids, Stem Borer, Armyworm</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>0.0001717609002568438</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Aphids, Rice Bug, Armyworm</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>0.0001698110023169601</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, None, Armyworm</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>0.0001675690126288744</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, None, Stem Borer, Aphids</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>0.0001655400804360697</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Stem Borer, Armyworm</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>0.0001651886266716899</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Aphids, Armyworm</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>0.0001648301158976988</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Rice Bug, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>0.0001627807390064265</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Rice Bug, Aphids, Armyworm</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0.00016160595103038</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Rice Bug, None, Armyworm</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0.0001608289505770041</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Stem Borer, Rice Bug, None</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>0.0001604880965102918</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Stem Borer, Rice Bug, Aphids</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0.0001591669670442723</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Aphids, Stem Borer, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>0.0001561218086078456</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Aphids, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>0.0001538458740797217</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, None, Rice Bug, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>0.0001483435261574543</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Armyworm, Rice Bug, None</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>0.0001429369242851029</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Aphids, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>0.0001425223458217002</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Rice Bug, None, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>0.000141095589784364</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Stem Borer, Armyworm, Aphids</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>0.0001387081779614268</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Armyworm, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>0.0001375123984221588</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Rice Bug, Stem Borer, Armyworm</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>0.0001355832943936967</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Stem Borer, Rice Bug, None</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>0.0001333250439148797</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Rice Bug, Stem Borer, None</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>0.0001310943583341602</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Stem Borer, Aphids, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>0.0001303974495134227</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Stem Borer, Rice Bug, Armyworm</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>0.0001268615765672975</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Armyworm, Aphids, None</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>0.0001259602795441273</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Armyworm, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>0.0001255331326133995</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, None, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>0.0001255216817387752</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Rice Bug, None, Aphids</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>0.0001248793998876363</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Stem Borer, Aphids</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>0.0001245973891270837</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, None, Armyworm, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>0.0001243606001851617</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, None, Rice Bug, Aphids</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>0.000117208290348342</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Armyworm, None, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>0.00011617643610334</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Aphids, None, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>0.0001158112947380661</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, None, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>0.0001157259618295161</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Rice Bug, Armyworm, None</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>0.0001155304594855683</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Aphids, Stem Borer, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>0.0001134597855428206</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Stem Borer, None, Aphids</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>0.0001121313200143646</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Armyworm, None, Aphids</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>0.0001097388577497324</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, None, Stem Borer, Aphids</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>0.0001080523225766881</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, None, Stem Borer, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>0.0001077887248452694</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Armyworm, None, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>0.0001077117599158344</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, None, Aphids, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>0.0001062261691351597</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Rice Bug, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>0.00010521646772756</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Rice Bug, None, Armyworm</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>0.0001049617757724417</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Stem Borer, Aphids, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>0.0001035576041427578</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Armyworm, None, Aphids</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>0.0001005113245236022</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Armyworm, Stem Borer, None</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>9.916705069585192e-05</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Rice Bug, Stem Borer, Armyworm</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>9.655264913422166e-05</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Rice Bug, Aphids, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>9.41770408886878e-05</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Stem Borer, None, Armyworm</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>9.196436966987092e-05</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Aphids, Rice Bug, Armyworm</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>8.960792534842458e-05</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Stem Borer, None, Armyworm</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>8.701096793328094e-05</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Rice Bug, Aphids, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>8.556362112904411e-05</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Stem Borer, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>8.41324580573003e-05</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Stem Borer, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>8.167752689958161e-05</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Armyworm, Rice Bug, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>7.931410296825779e-05</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Stem Borer, Armyworm, None</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>7.526159766431289e-05</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Armyworm, None, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>7.275352732577198e-05</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Rice Bug, None</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>6.889933955715963e-05</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Armyworm, None, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>6.825970296698002e-05</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, None, Aphids, Armyworm</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>6.419514303421773e-05</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Armyworm, Rice Bug, None</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>6.218215208331202e-05</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Stem Borer, Armyworm</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>6.081276568075594e-05</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Aphids, Stem Borer, None</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>5.9612748504807e-05</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Aphids, Armyworm, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>5.546959260121208e-05</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, None, Aphids, Armyworm</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>5.479785104221092e-05</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Aphids, Rice Bug, None</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>5.279049587246815e-05</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Aphids, None, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>5.196767101931517e-05</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Rice Bug, Armyworm, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>4.833624453377353e-05</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Rice Bug, Stem Borer, None</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>4.799174051086017e-05</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, Aphids, None, Armyworm</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>4.2015550165016e-05</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Armyworm, Stem Borer, Aphids</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>4.12273191153619e-05</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Aphids, Rice Bug, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>4.079374623400854e-05</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, None, Aphids, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>3.949820824083374e-05</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>cat__Pest_Stem Borer, Rice Bug, None</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>3.842897496610587e-05</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Aphids, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>3.829316835335383e-05</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>cat__Pest_Rice Bug, None, Armyworm, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>3.220001103754393e-05</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, None, Armyworm, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>2.074362854657897e-05</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, None, Armyworm, Stem Borer</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>1.723821017957366e-05</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>cat__Pest_Armyworm, Stem Borer, None, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1.478916383543255e-05</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Stem Borer, Armyworm, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>1.289753131749621e-05</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>cat__Pest_Aphids, Armyworm, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>1.251279268565747e-05</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>cat__Pest_None, Aphids, Armyworm, Rice Bug</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>7.040808781941092e-06</v>
       </c>
     </row>
   </sheetData>

--- a/feature_importance.xlsx
+++ b/feature_importance.xlsx
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4851700743349603</v>
+        <v>0.5012422132172031</v>
       </c>
     </row>
     <row r="3">
@@ -445,27 +445,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3423108388188704</v>
+        <v>0.3543330909836149</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>num__Average Selling Price (₱/kg)</t>
+          <t>num__Farm Size (ha)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07725192263298186</v>
+        <v>0.06366537794434481</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>num__Farm Size (ha)</t>
+          <t>num__Average Selling Price (₱/kg)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07584388938853436</v>
+        <v>0.05995478397746684</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01015234101858871</v>
+        <v>0.01161238049932227</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009270933806064448</v>
+        <v>0.009192153378047999</v>
       </c>
     </row>
     <row r="8">

--- a/feature_importance.xlsx
+++ b/feature_importance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,71 +431,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>num__Crop Yield (bags/ha)</t>
+          <t>Crop Yield (bags/ha)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5012422132172031</v>
+        <v>0.5187680535436274</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>num__Feedback Score</t>
+          <t>Feedback Score</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3543330909836149</v>
+        <v>0.3719445947201526</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>num__Farm Size (ha)</t>
+          <t>Farm Size (ha)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06366537794434481</v>
+        <v>0.04921832999709233</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>num__Average Selling Price (₱/kg)</t>
+          <t>Average Selling Price (₱/kg)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05995478397746684</v>
+        <v>0.04227595235226127</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cat__Subsidy Received_Yes</t>
+          <t>Subsidy Received</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01161238049932227</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cat__Subsidy Received_No</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.009192153378047999</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>num__Average Yield (bags/ha)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
+        <v>0.01779306938686629</v>
       </c>
     </row>
   </sheetData>

--- a/feature_importance.xlsx
+++ b/feature_importance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5187680535436274</v>
+        <v>0.48802190332314</v>
       </c>
     </row>
     <row r="3">
@@ -445,37 +445,47 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3719445947201526</v>
+        <v>0.3685344674319745</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Farm Size (ha)</t>
+          <t>Average Yield (bags/ha)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04921832999709233</v>
+        <v>0.0465477558619115</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Average Selling Price (₱/kg)</t>
+          <t>Farm Size (ha)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04227595235226127</v>
+        <v>0.04105147163881072</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Average Selling Price (₱/kg)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.03851462346295439</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Subsidy Received</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0.01779306938686629</v>
+      <c r="B7" t="n">
+        <v>0.01732977828120869</v>
       </c>
     </row>
   </sheetData>

--- a/feature_importance.xlsx
+++ b/feature_importance.xlsx
@@ -1,81 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Feature</t>
-  </si>
-  <si>
-    <t>Importance</t>
-  </si>
-  <si>
-    <t>Crop Yield (bags/ha)</t>
-  </si>
-  <si>
-    <t>Feedback Score</t>
-  </si>
-  <si>
-    <t>Average Yield (bags/ha)</t>
-  </si>
-  <si>
-    <t>Farm Size (ha)</t>
-  </si>
-  <si>
-    <t>Average Selling Price (₱/kg)</t>
-  </si>
-  <si>
-    <t>Subsidy Received</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -87,34 +46,81 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -123,10 +129,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -164,71 +170,69 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -252,53 +256,54 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="51000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="94000"/>
+                <a:shade val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="9500"/>
+              <a:shade val="95000"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -308,7 +313,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -317,7 +322,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -326,7 +331,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -334,10 +339,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -366,7 +371,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="20000"/>
+                <a:shade val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -379,12 +384,13 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
+                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -402,74 +408,87 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" style="4" width="24.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3">
-        <v>0.48802190332314</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3">
-        <v>0.368534467431975</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0.046547755861912</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="3">
-        <v>0.041051471638811</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="3">
-        <v>0.038514623462954</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="3">
-        <v>0.017329778281209</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Importance</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Crop Yield (tons)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.3207374719509528</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Average Yield (tons/ha)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.2012360525484539</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Farm Size (ha)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.1869291392187165</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Feedback Score</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.1668336117736807</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Subsidy Received</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.08040106275018061</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Average Selling Price (₱/kg)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.04386266175801546</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/feature_importance.xlsx
+++ b/feature_importance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,61 +431,151 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Crop Yield (tons)</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3207374719509528</v>
+        <v>0.09883334771208538</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Average Yield (tons/ha)</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2012360525484539</v>
+        <v>0.09855622228067518</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Farm Size (ha)</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1869291392187165</v>
+        <v>0.09595566203960906</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Feedback Score</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1668336117736807</v>
+        <v>0.08156158927578479</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Subsidy Received</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08040106275018061</v>
+        <v>0.07911978456501695</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.07849286568426983</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.07054545611560033</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0693953816930319</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.06932170808463967</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Average Selling Price (₱/kg)</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0.04386266175801546</v>
+      <c r="B11" t="n">
+        <v>0.06494624775548256</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.06477202788439515</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Crop Yield (tons)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.0399201860076183</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Farm Size (ha)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.03682730917625671</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Average Yield (tons/ha)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.0360100767779746</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Subsidy Received</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.01574213494755949</v>
       </c>
     </row>
   </sheetData>
